--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0024.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0024.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Xem lại các màn chơi hiện tại tại đây.</t>
+          <t>Xem lại màn chơi hiện tại tại đây.</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
@@ -647,7 +647,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Xem lại các màn chơi hiện tại tại đây.</t>
+          <t>Xem lại màn chơi hiện tại tại đây.</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Xem lại các màn chơi hiện tại tại đây.</t>
+          <t>Xem lại màn chơi hiện tại tại đây.</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
@@ -779,7 +779,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Event để nhận phần thưởng giới hạn thời gian.</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện để nhận phần thưởng giới hạn thời gian.</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr"/>
@@ -845,7 +845,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Event để nhận phần thưởng giới hạn thời gian.</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện để nhận phần thưởng giới hạn thời gian.</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Event để nhận phần thưởng giới hạn thời gian.</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện để nhận phần thưởng giới hạn thời gian.</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Bạn có thể xem thông tin chi tiết về bản nhạc và cơ chế tại đây.</t>
+          <t>Bạn có thể xem thông tin chi tiết về đường đua và cơ chế tại đây</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Bạn có thể xem thông tin chi tiết về bản nhạc và cơ chế tại đây.</t>
+          <t>Bạn có thể xem thông tin chi tiết về đường đua và cơ chế tại đây</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Bạn có thể xem thông tin chi tiết về bản nhạc và cơ chế tại đây.</t>
+          <t>Bạn có thể xem thông tin chi tiết về đường đua và cơ chế tại đây</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Trong trận đấu, các cơ chế có thể gây ảnh hưởng tích cực hoặc tiêu cực lên Khối Lập Phương.</t>
+          <t>Trong trận đấu, các cơ chế có thể mang lại hiệu ứng tích cực hoặc tiêu cực cho Cube.</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr"/>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Trong trận đấu, các cơ chế có thể gây ảnh hưởng tích cực hoặc tiêu cực lên Khối Lập Phương.</t>
+          <t>Trong trận đấu, các cơ chế có thể mang lại hiệu ứng tích cực hoặc tiêu cực cho Cube.</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Trong trận đấu, các cơ chế có thể gây ảnh hưởng tích cực hoặc tiêu cực lên Khối Lập Phương.</t>
+          <t>Trong trận đấu, các cơ chế có thể mang lại hiệu ứng tích cực hoặc tiêu cực cho Cube.</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr"/>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Trong Illusive Realm, bạn có thể chọn một Illusive Echo để hỗ trợ trong chiến đấu.</t>
+          <t>Trong Vực Ảo Mộng, ngươi có thể chọn một Ảo Ảnh để hỗ trợ trong trận chiến.</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Trong Illusive Realm, bạn có thể chọn một Illusive Echo để hỗ trợ trong chiến đấu.</t>
+          <t>Trong Vực Ảo Mộng, ngươi có thể chọn một Ảo Ảnh để hỗ trợ trong trận chiến.</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Trong Illusive Realm, bạn có thể chọn một Illusive Echo để hỗ trợ trong chiến đấu.</t>
+          <t>Trong Vực Ảo Mộng, ngươi có thể chọn một Ảo Ảnh để hỗ trợ trong trận chiến.</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch và Dodge các đòn tấn công của chúng để tăng Cấp Độ Giao Hưởng.</t>
+          <t>Gây sát thương lên kẻ địch và né đòn của chúng để tăng Cấp Giao Hưởng.</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch và Dodge các đòn tấn công của chúng để tăng Cấp Độ Giao Hưởng.</t>
+          <t>Gây sát thương lên kẻ địch và né đòn của chúng để tăng Cấp Giao Hưởng.</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch và Dodge các đòn tấn công của chúng để tăng Cấp Độ Giao Hưởng.</t>
+          <t>Gây sát thương lên kẻ địch và né đòn của chúng để tăng Cấp Giao Hưởng.</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr"/>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Phép ẩn dụ cung cấp buff đặc biệt và Quả Cầu Thuộc Tính.</t>
+          <t>Ẩn Dụ cung cấp hiệu ứng đặc biệt và Quả Cầu Thuộc Tính.</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Phép ẩn dụ cung cấp buff đặc biệt và Quả Cầu Thuộc Tính.</t>
+          <t>Ẩn Dụ cung cấp hiệu ứng đặc biệt và Quả Cầu Thuộc Tính.</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr"/>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Phép ẩn dụ cung cấp buff đặc biệt và Quả Cầu Thuộc Tính.</t>
+          <t>Ẩn Dụ cung cấp hiệu ứng đặc biệt và Quả Cầu Thuộc Tính.</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Thu thập đủ số lượng Quả Cầu Thuộc Tính khác nhau để mở khóa thêm khả năng của Illusive Echo.</t>
+          <t>Thu thập đủ số lượng Vật Phẩm Thuộc Tính khác nhau để mở khóa thêm kỹ năng của Illusive Echo</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Thu thập đủ số lượng Quả Cầu Thuộc Tính khác nhau để mở khóa thêm khả năng của Illusive Echo.</t>
+          <t>Thu thập đủ số lượng Vật Phẩm Thuộc Tính khác nhau để mở khóa thêm kỹ năng của Illusive Echo</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Thu thập đủ số lượng Quả Cầu Thuộc Tính khác nhau để mở khóa thêm khả năng của Illusive Echo.</t>
+          <t>Thu thập đủ số lượng Vật Phẩm Thuộc Tính khác nhau để mở khóa thêm kỹ năng của Illusive Echo</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr"/>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Thu thập đủ số lượng Quả Cầu Thuộc Tính khác nhau để mở khóa thêm khả năng của Illusive Echo.</t>
+          <t>Thu thập đủ số lượng Vật Phẩm Thuộc Tính khác nhau để mở khóa thêm kỹ năng của Illusive Echo</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Thu thập đủ số lượng Quả Cầu Thuộc Tính khác nhau để mở khóa thêm khả năng của Illusive Echo.</t>
+          <t>Thu thập đủ số lượng Vật Phẩm Thuộc Tính khác nhau để mở khóa thêm kỹ năng của Illusive Echo</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Thu thập đủ số lượng Quả Cầu Thuộc Tính khác nhau để mở khóa thêm khả năng của Illusive Echo.</t>
+          <t>Thu thập đủ số lượng Vật Phẩm Thuộc Tính khác nhau để mở khóa thêm kỹ năng của Illusive Echo</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Khi Năng Lượng của bạn đầy, bạn có thể biến hình thành Crownless.</t>
+          <t>Khi Năng Lượng của cậu đầy, cậu có thể biến hình thành Crownless.</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Khi Năng Lượng của bạn đầy, bạn có thể biến hình thành Crownless.</t>
+          <t>Khi Năng Lượng của cậu đầy, cậu có thể biến hình thành Crownless.</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Chọn "Tăng Cường Resonator" để cấp cho Resonator một khả năng đặc biệt không có ngoài sự kiện này.</t>
+          <t>Chọn "Resonator Enhancement" để trao cho Resonator một khả năng đặc biệt không có ngoài sự kiện này.</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Chọn "Tăng Cường Resonator" để cấp cho Resonator một khả năng đặc biệt không có ngoài sự kiện này.</t>
+          <t>Chọn "Resonator Enhancement" để trao cho Resonator một khả năng đặc biệt không có ngoài sự kiện này.</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Chọn "Tăng Cường Resonator" để cấp cho Resonator một khả năng đặc biệt không có ngoài sự kiện này.</t>
+          <t>Chọn "Resonator Enhancement" để trao cho Resonator một khả năng đặc biệt không có ngoài sự kiện này.</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr"/>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Token cung cấp hiệu ứng buff đặc biệt.</t>
+          <t>Mã thông báo cung cấp những hiệu ứng tăng cường đặc biệt.</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Token cung cấp hiệu ứng buff đặc biệt.</t>
+          <t>Mã thông báo cung cấp những hiệu ứng tăng cường đặc biệt.</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr"/>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Token cung cấp hiệu ứng buff đặc biệt.</t>
+          <t>Mã thông báo cung cấp những hiệu ứng tăng cường đặc biệt.</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem tất cả hiệu ứng tăng cường đã nhận.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem tất cả hiệu ứng tăng cường đã nhận.</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr"/>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=Ấn} {0}+{1} để xem tất cả hiệu ứng tăng cường đã nhận.</t>
+          <t>Nhấn {0}+{1} để xem tất cả hiệu ứng tăng cường đã nhận.</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem tất cả hiệu ứng tăng cường đã nhận.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem tất cả hiệu ứng tăng cường đã nhận.</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr"/>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Quả Cầu Attribute cũng tăng thêm thuộc tính thưởng.</t>
+          <t>Viên Thuộc tính cũng cấp thêm thưởng Thuộc tính</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Quả Cầu Attribute cũng tăng thêm thuộc tính thưởng.</t>
+          <t>Viên Thuộc tính cũng cấp thêm thưởng Thuộc tính</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Quả Cầu Attribute cũng tăng thêm thuộc tính thưởng.</t>
+          <t>Viên Thuộc tính cũng cấp thêm thưởng Thuộc tính</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Concerto Companions sẽ tung Resonance Liberation khi được triệu hồi.</t>
+          <t>Đồng Hành Giao Hưởng sẽ thi triển Resonance Liberation khi được triệu hồi.</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr"/>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Concerto Companions sẽ tung Resonance Liberation khi được triệu hồi.</t>
+          <t>Đồng Hành Giao Hưởng sẽ thi triển Resonance Liberation khi được triệu hồi.</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr"/>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>Concerto Companions sẽ tung Resonance Liberation khi được triệu hồi.</t>
+          <t>Đồng Hành Giao Hưởng sẽ thi triển Resonance Liberation khi được triệu hồi.</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Tiếp tục thách đấu Độ sâu Ảo ảnh để nhận thưởng như Astrite.</t>
+          <t>Hãy tiếp tục thách thức Depths of Illusive Realm để nhận thưởng như Astrite.</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr"/>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Tiếp tục thách đấu Độ sâu Ảo ảnh để nhận thưởng như Astrite.</t>
+          <t>Hãy tiếp tục thách thức Depths of Illusive Realm để nhận thưởng như Astrite.</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr"/>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Tiếp tục thách đấu Độ sâu Ảo ảnh để nhận thưởng như Astrite.</t>
+          <t>Hãy tiếp tục thách thức Depths of Illusive Realm để nhận thưởng như Astrite.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr"/>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Hãy tiếp tục thử thách để trải nghiệm các Echoes Ảo khác nhau!</t>
+          <t>Hãy tiếp tục thử thách với những Ảo Ảnh Tiếng Vọng khác nhau đi!</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr"/>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Hãy tiếp tục thử thách để trải nghiệm các Echoes Ảo khác nhau!</t>
+          <t>Hãy tiếp tục thử thách với những Ảo Ảnh Tiếng Vọng khác nhau đi!</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Hãy tiếp tục thử thách để trải nghiệm các Echoes Ảo khác nhau!</t>
+          <t>Hãy tiếp tục thử thách với những Ảo Ảnh Tiếng Vọng khác nhau đi!</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr"/>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để bắt đầu thử thách.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu thử thách.</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr"/>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để bắt đầu thử thách.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu thử thách.</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr"/>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để bắt đầu thử thách.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu thử thách.</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Tuning Ngữ Nghĩa áp dụng nhiều hạn chế khác nhau trong trận đấu để tăng độ khó thử thách.</t>
+          <t>Điều Chỉnh Memetic áp dụng nhiều hạn chế trong chiến đấu để tăng độ khó thử thách.</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr"/>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Tuning Ngữ Nghĩa áp dụng nhiều hạn chế khác nhau trong trận đấu để tăng độ khó thử thách.</t>
+          <t>Điều Chỉnh Memetic áp dụng nhiều hạn chế trong chiến đấu để tăng độ khó thử thách.</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr"/>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Tuning Ngữ Nghĩa áp dụng nhiều hạn chế khác nhau trong trận đấu để tăng độ khó thử thách.</t>
+          <t>Điều Chỉnh Memetic áp dụng nhiều hạn chế trong chiến đấu để tăng độ khó thử thách.</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr"/>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy, bạn có thể sử dụng Resonance Liberation của Concerto Companion.</t>
+          <t>Khi Concerto Energy đầy, bạn có thể kích hoạt Resonance Liberation của Cộng Sự Concerto.</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr"/>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy, bạn có thể sử dụng Resonance Liberation của Concerto Companion.</t>
+          <t>Khi Concerto Energy đầy, bạn có thể kích hoạt Resonance Liberation của Cộng Sự Concerto.</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy, bạn có thể sử dụng Resonance Liberation của Concerto Companion.</t>
+          <t>Khi Concerto Energy đầy, bạn có thể kích hoạt Resonance Liberation của Cộng Sự Concerto.</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr"/>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu thử thách khi đã sẵn sàng.</t>
+          <t>Bắt đầu thử thách khi nào sẵn sàng nhé.</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr"/>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu thử thách khi đã sẵn sàng.</t>
+          <t>Bắt đầu thử thách khi nào sẵn sàng nhé.</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr"/>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu thử thách khi đã sẵn sàng.</t>
+          <t>Bắt đầu thử thách khi nào sẵn sàng nhé.</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr"/>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>Tỉ lệ Phần thưởng càng cao, độ khó càng lớn.</t>
+          <t>Tỷ lệ Phần thưởng cao hơn đồng nghĩa với độ khó lớn hơn.</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr"/>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Tỉ lệ Phần thưởng càng cao, độ khó càng lớn.</t>
+          <t>Tỷ lệ Phần thưởng cao hơn đồng nghĩa với độ khó lớn hơn.</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr"/>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Tỉ lệ Phần thưởng càng cao, độ khó càng lớn.</t>
+          <t>Tỷ lệ Phần thưởng cao hơn đồng nghĩa với độ khó lớn hơn.</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Dùng Memory Points kiếm được từ thử thách để mua ưu đãi trong Thought Evolution.</t>
+          <t>Mua các phần thưởng tăng cường trong Tiến Hóa Ý Niệm bằng Điểm Ký Ức kiếm được từ thử thách.</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr"/>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Dùng Memory Points kiếm được từ thử thách để mua ưu đãi trong Thought Evolution.</t>
+          <t>Mua các phần thưởng tăng cường trong Tiến Hóa Ý Niệm bằng Điểm Ký Ức kiếm được từ thử thách.</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr"/>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Dùng Memory Points kiếm được từ thử thách để mua ưu đãi trong Thought Evolution.</t>
+          <t>Mua các phần thưởng tăng cường trong Tiến Hóa Ý Niệm bằng Điểm Ký Ức kiếm được từ thử thách.</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Buffs sẽ tăng cường khả năng của Resonators trong Illusive Realm.</t>
+          <t>Buff sẽ tăng cường khả năng của Resonator trong Illusive Realm.</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr"/>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Buffs sẽ tăng cường khả năng của Resonators trong Illusive Realm.</t>
+          <t>Buff sẽ tăng cường khả năng của Resonator trong Illusive Realm.</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr"/>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Buffs sẽ tăng cường khả năng của Resonators trong Illusive Realm.</t>
+          <t>Buff sẽ tăng cường khả năng của Resonator trong Illusive Realm.</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr"/>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>{0} Dùng bùa Sigrika đã khắc cho bạn để cảm nhận mảnh vỡ bùa Royan gần đó.</t>
+          <t>Dùng ký tự Sigrika đã được khắc cho ngươi để cảm nhận những mảnh vỡ ký tự Royan gần đây.</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr"/>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Dùng ký tự Sigrika đã khắc cho bạn để cảm nhận các mảnh ký tự Royan gần đó.</t>
+          <t>Dùng Sigrika, biểu tượng được khắc riêng cho ngươi, để cảm nhận những mảnh vỡ Royan gần đó.</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr"/>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để vào Star Bouncing.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để vào Star Bouncing.</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr"/>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để vào Star Bouncing.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để vào Star Bouncing.</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr"/>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để vào Star Bouncing.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để vào Star Bouncing.</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr"/>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>Enter trang chuẩn bị và chọn Persona Pinball để triển khai.</t>
+          <t>Vào trang chuẩn bị và chọn triển khai Persona Pinball.</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr"/>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} {0} để vào trang chuẩn bị và chọn Persona Pinball để triển khai.</t>
+          <t>Nhấn {0} để vào trang chuẩn bị và chọn Persona Pinball triển khai.</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr"/>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>Enter trang chuẩn bị và chọn Persona Pinball để triển khai.</t>
+          <t>Vào trang chuẩn bị và chọn triển khai Persona Pinball.</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr"/>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Begin giai đoạn đầu tiên.</t>
+          <t>Bắt đầu giai đoạn đầu tiên.</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr"/>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} {0} để bắt đầu giai đoạn đầu tiên.</t>
+          <t>Nhấn {0} để bắt đầu giai đoạn đầu tiên.</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr"/>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Begin giai đoạn đầu tiên.</t>
+          <t>Bắt đầu giai đoạn đầu tiên.</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr"/>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=Dùng} Flipper để bắn Persona Pinball và tấn công kẻ địch.</t>
+          <t>Dùng Cần Gạt để bắn Bi Nhân Cách, tấn công kẻ địch.</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr"/>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=Dùng} {0} Flippers để bắn Persona Pinball và tấn công kẻ địch.</t>
+          <t>Dùng {0} Cần Gạt để bắn Bi Nhân Cách, tấn công kẻ địch.</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=Dùng} Flipper để bắn Persona Pinball và tấn công kẻ địch.</t>
+          <t>Dùng Cần Gạt để bắn Bi Nhân Cách, tấn công kẻ địch.</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr"/>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Khi Pinball đang di chuyển, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Rush để đẩy nó lao vào kẻ địch.</t>
+          <t>Khi Quả Cầu Pinball đang di chuyển, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Rush để phóng nó lao thẳng vào kẻ địch.</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr"/>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>Khi Bóng Bàn đang di chuyển, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để Xông Tới và đẩy bóng về phía kẻ địch.</t>
+          <t>Khi Quả Cầu Pinball đang di chuyển, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} Rush để phóng nó lao thẳng vào kẻ địch.</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr"/>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Khi Pinball đang di chuyển, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Rush để đẩy nó lao vào kẻ địch.</t>
+          <t>Khi Quả Cầu Pinball đang di chuyển, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Rush để phóng nó lao thẳng vào kẻ địch.</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr"/>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>Khi năng lượng của Pinball đã đầy, {Cus:Ipt,Touch=Touch PC=press Gamepad=Ấn} để tung ra kỹ năng mạnh.</t>
+          <t>Khi năng lượng của Pinball đã đầy, {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để giải phóng kỹ năng mạnh mẽ.</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr"/>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>Khi năng lượng của Pinball đã đầy, {Cus:Ipt,Touch=Touch PC=press Gamepad=Ấn} để tung ra kỹ năng mạnh.</t>
+          <t>Khi năng lượng của Pinball đã đầy, {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để giải phóng kỹ năng mạnh mẽ.</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr"/>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>Khi năng lượng của Pinball đã đầy, {Cus:Ipt,Touch=Touch PC=press Gamepad=Ấn} để tung ra kỹ năng mạnh.</t>
+          <t>Khi năng lượng của Pinball đã đầy, {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để giải phóng kỹ năng mạnh mẽ.</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr"/>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Enter trang chuẩn bị và triển khai Persona Pinball mới.</t>
+          <t>Vào trang chuẩn bị và triển khai Persona Pinball mới.</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr"/>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>Enter trang chuẩn bị và triển khai Persona Pinball mới.</t>
+          <t>Vào trang chuẩn bị và triển khai Persona Pinball mới.</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr"/>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Enter trang chuẩn bị và triển khai Persona Pinball mới.</t>
+          <t>Vào trang chuẩn bị và triển khai Persona Pinball mới.</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>Chọn Persona Pinball mới được mở khóa.</t>
+          <t>Chọn Persona Pinball vừa mở khóa.</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr"/>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Chọn Persona Pinball mới được mở khóa.</t>
+          <t>Chọn Persona Pinball vừa mở khóa.</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr"/>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>Chọn Persona Pinball mới được mở khóa.</t>
+          <t>Chọn Persona Pinball vừa mở khóa.</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr"/>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để xác nhận đội hình.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xác nhận đội hình.</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr"/>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} {0} để xác nhận đội hình.</t>
+          <t>Nhấn {0} để xác nhận đội hình.</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để xác nhận đội hình.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xác nhận đội hình.</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr"/>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>Persona Pinball ở Slot 1 có thể kích hoạt Kỹ Năng Leader.</t>
+          <t>Persona Pinball ở Khe 1 có thể kích hoạt Kỹ Năng Đội Trưởng.</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr"/>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>{0} Persona Pinball ở Vị trí 1 có thể kích hoạt Kỹ Năng Leader.</t>
+          <t>{0} Bi Persona Pinball ở Khe 1 có thể kích hoạt Kỹ Năng Thủ Lĩnh.</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr"/>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>Persona Pinball ở Slot 1 có thể kích hoạt Kỹ Năng Leader.</t>
+          <t>Persona Pinball ở Khe 1 có thể kích hoạt Kỹ Năng Đội Trưởng.</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr"/>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>Xem thông tin kẻ địch cho giai đoạn hiện tại tại đây.</t>
+          <t>Xem thông tin kẻ địch trong giai đoạn hiện tại tại đây.</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr"/>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>Xem thông tin kẻ địch cho giai đoạn hiện tại tại đây.</t>
+          <t>Xem thông tin kẻ địch trong giai đoạn hiện tại tại đây.</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr"/>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>Có thể thử thách lại giai đoạn này nhiều lần để nhận điểm thưởng.</t>
+          <t>Giai đoạn này có thể thách đấu nhiều lần để nhận điểm thưởng.</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr"/>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>Có thể thử thách lại giai đoạn này nhiều lần để nhận điểm thưởng.</t>
+          <t>Giai đoạn này có thể thách đấu nhiều lần để nhận điểm thưởng.</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr"/>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>Có thể thử thách lại giai đoạn này nhiều lần để nhận điểm thưởng.</t>
+          <t>Giai đoạn này có thể thách đấu nhiều lần để nhận điểm thưởng.</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>Đạt tổng điểm mục tiêu để nhận phần thưởng mốc.</t>
+          <t>Đạt tổng điểm mục tiêu để nhận thưởng cột mốc.</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr"/>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>Đạt tổng điểm mục tiêu để nhận phần thưởng mốc.</t>
+          <t>Đạt tổng điểm mục tiêu để nhận thưởng cột mốc.</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr"/>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>Đạt tổng điểm mục tiêu để nhận phần thưởng mốc.</t>
+          <t>Đạt tổng điểm mục tiêu để nhận thưởng cột mốc.</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr"/>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>Mở trang Persona Pinball để xem và nâng cấp Pinball của bạn.</t>
+          <t>Mở trang Persona Pinball để xem và nâng cấp các Pinball của cậu.</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr"/>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>{0} Mở trang Persona Pinball để xem và nâng cấp Pinball của bạn.</t>
+          <t>Mở trang Persona Pinball để xem và nâng cấp Pinball của bạn.</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr"/>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>Mở trang Persona Pinball để xem và nâng cấp Pinball của bạn.</t>
+          <t>Mở trang Persona Pinball để xem và nâng cấp các Pinball của cậu.</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr"/>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để nâng cấp Persona Pinball và tăng chỉ số của nó.</t>
+          <t>Nhấn vào đây để nâng cấp một Persona Pinball và tăng chỉ số của nó.</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr"/>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để nâng cấp Persona Pinball và tăng chỉ số của nó.</t>
+          <t>Nhấn vào đây để nâng cấp một Persona Pinball và tăng chỉ số của nó.</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr"/>
@@ -8513,7 +8513,7 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để nâng cấp Persona Pinball và tăng chỉ số của nó.</t>
+          <t>Nhấn vào đây để nâng cấp một Persona Pinball và tăng chỉ số của nó.</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr"/>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>Enter Stardock Market để mua Tactical ROM.</t>
+          <t>Vào Chợ Stardock để mua ROM Chiến thuật</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>Press {0} to enter Stardock Market mua Tactical ROM.</t>
+          <t>Nhấn {0} để vào Chợ Stardock mua ROM Chiến Thuật</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr"/>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>Enter Stardock Market để mua Tactical ROM.</t>
+          <t>Vào Chợ Stardock để mua ROM Chiến thuật</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr"/>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>Tham gia Galaxy Forage Tour để nhận thử thách phần thưởng có thể lặp lại.</t>
+          <t>Tham gia Tour Thám Hiểm Thiên Hà để nhận thưởng thử thách lặp lại.</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr"/>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>{0} Tham gia Galaxy Forage Tour để nhận thưởng thử thách có thể lặp lại.</t>
+          <t>{0} Tham gia Thám Hiểm Dải Ngân Hà để nhận thưởng lặp lại từ thử thách.</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr"/>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>Tham gia Galaxy Forage Tour để nhận thử thách phần thưởng có thể lặp lại.</t>
+          <t>Tham gia Tour Thám Hiểm Thiên Hà để nhận thưởng thử thách lặp lại.</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr"/>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} nút Persona Pinball để trang bị Tactical ROM.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút Persona Pinball để trang bị ROM Chiến Thuật.</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr"/>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} nút Persona Pinball để trang bị Tactical ROM.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút Persona Pinball để trang bị ROM Chiến Thuật.</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr"/>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} nút Persona Pinball để trang bị Tactical ROM.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút Persona Pinball để trang bị ROM Chiến Thuật.</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr"/>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để chuyển sang tab Tactical ROM.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chuyển sang tab ROM Chiến Thuật.</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr"/>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để chuyển sang tab Tactical ROM.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chuyển sang tab ROM Chiến Thuật.</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr"/>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để chuyển sang tab Tactical ROM.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chuyển sang tab ROM Chiến Thuật.</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr"/>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>Mở kho ROM để chọn và trang bị Tactical ROM.</t>
+          <t>Mở kho ROM để chọn và trang bị ROM Chiến Thuật.</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>Mở kho ROM để chọn và trang bị Tactical ROM.</t>
+          <t>Mở kho ROM để chọn và trang bị ROM Chiến Thuật.</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr"/>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>Mở kho ROM để chọn và trang bị Tactical ROM.</t>
+          <t>Mở kho ROM để chọn và trang bị ROM Chiến Thuật.</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr"/>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>Mỗi Tactical ROM có một chỉ số Chính cố định và các chỉ số Phụ ngẫu nhiên.</t>
+          <t>Mỗi ROM Chiến Thuật đều có một Chỉ Số Chính cố định và các Chỉ Số Phụ ngẫu nhiên.</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>Mỗi Tactical ROM có một chỉ số Chính cố định và các chỉ số Phụ ngẫu nhiên.</t>
+          <t>Mỗi ROM Chiến Thuật đều có một Chỉ Số Chính cố định và các Chỉ Số Phụ ngẫu nhiên.</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr"/>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>Mỗi Tactical ROM có một chỉ số Chính cố định và các chỉ số Phụ ngẫu nhiên.</t>
+          <t>Mỗi ROM Chiến Thuật đều có một Chỉ Số Chính cố định và các Chỉ Số Phụ ngẫu nhiên.</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr"/>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để trang bị cho Persona Pinball hiện tại</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để trang bị cho Persona Pinball hiện tại.</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr"/>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để trang bị cho Persona Pinball hiện tại</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để trang bị cho Persona Pinball hiện tại.</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để trang bị cho Persona Pinball hiện tại</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để trang bị cho Persona Pinball hiện tại.</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr"/>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để chuyển đến thử thách Đường Đua Vô Tận Dải Ngân Hà.</t>
+          <t>Nhấn vào đây để chuyển thẳng đến thử thách Đường Đua Thiên Hà Vô Tận.</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr"/>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để chuyển đến thử thách Đường Đua Vô Tận Dải Ngân Hà.</t>
+          <t>Nhấn vào đây để chuyển thẳng đến thử thách Đường Đua Thiên Hà Vô Tận.</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr"/>
@@ -10295,7 +10295,7 @@
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để chuyển đến thử thách Đường Đua Vô Tận Dải Ngân Hà.</t>
+          <t>Nhấn vào đây để chuyển thẳng đến thử thách Đường Đua Thiên Hà Vô Tận.</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr"/>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Nhấp Tay cầm=Nhấn} vào đây để giải mã thêm Tactical ROM.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để giải mã thêm ROM Chiến Thuật.</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr"/>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} {0} để giải mã thêm Tactical ROM.</t>
+          <t>Nhấn {0} để giải mã thêm ROM Chiến Thuật.</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr"/>
@@ -10493,7 +10493,7 @@
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Nhấp Tay cầm=Nhấn} vào đây để giải mã thêm Tactical ROM.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để giải mã thêm ROM Chiến Thuật.</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr"/>
@@ -10559,7 +10559,7 @@
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>Xem tiến độ khảo sát tại Khe Nứt Bịt Kín.</t>
+          <t>Xem tiến độ khảo sát tại Khe Nứt Niêm Phong.</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr"/>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>Xem tiến độ khảo sát tại Khe Nứt Bịt Kín.</t>
+          <t>Xem tiến độ khảo sát tại Khe Nứt Niêm Phong.</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr"/>
@@ -10691,7 +10691,7 @@
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>Xem tiến độ khảo sát tại Khe Nứt Bịt Kín.</t>
+          <t>Xem tiến độ khảo sát tại Khe Nứt Niêm Phong.</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr"/>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>Đến vị trí mục tiêu và điều tra.</t>
+          <t>Đến địa điểm mục tiêu và điều tra.</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr"/>
@@ -10823,7 +10823,7 @@
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>Đến vị trí mục tiêu và điều tra.</t>
+          <t>Đến địa điểm mục tiêu và điều tra.</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr"/>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>Đến vị trí mục tiêu và điều tra.</t>
+          <t>Đến địa điểm mục tiêu và điều tra.</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr"/>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>Hoàn thành Survey Tasks để nhận được lượng lớn vật liệu Restoration.</t>
+          <t>Hoàn thành Nhiệm Vụ Khảo Sát để nhận lượng lớn vật liệu Phục Hồi.</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr"/>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>Hoàn thành Survey Tasks để nhận được lượng lớn vật liệu Restoration.</t>
+          <t>Hoàn thành Nhiệm Vụ Khảo Sát để nhận lượng lớn vật liệu Phục Hồi.</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr"/>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>Hoàn thành Survey Tasks để nhận được lượng lớn vật liệu Restoration.</t>
+          <t>Hoàn thành Nhiệm Vụ Khảo Sát để nhận lượng lớn vật liệu Phục Hồi.</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr"/>
@@ -11153,7 +11153,7 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>Hiển thị tiến độ thu thập vật liệu hiện tại của bạn.</t>
+          <t>Đây là tiến độ thu thập nguyên liệu hiện tại của cậu.</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr"/>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>Hiển thị tiến độ thu thập vật liệu hiện tại của bạn.</t>
+          <t>Đây là tiến độ thu thập nguyên liệu hiện tại của cậu.</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr"/>
@@ -11285,7 +11285,7 @@
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>Hiển thị tiến độ thu thập vật liệu hiện tại của bạn.</t>
+          <t>Đây là tiến độ thu thập nguyên liệu hiện tại của cậu.</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr"/>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>Đã thu thập đủ tất cả vật liệu cần thiết cho Restoration. Tiến hành giao nộp.</t>
+          <t>Tất cả vật liệu cần thiết cho Phục Hồi đã được thu thập. Tiến hành chuyển giao.</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr"/>
@@ -11417,7 +11417,7 @@
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>Đã thu thập đủ tất cả vật liệu cần thiết cho Restoration. Tiến hành giao nộp.</t>
+          <t>Tất cả vật liệu cần thiết cho Phục Hồi đã được thu thập. Tiến hành chuyển giao.</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>Đã thu thập đủ tất cả vật liệu cần thiết cho Restoration. Tiến hành giao nộp.</t>
+          <t>Tất cả vật liệu cần thiết cho Phục Hồi đã được thu thập. Tiến hành chuyển giao.</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>Khi Restoration đạt đến một mốc nhất định, hãy đến Trại Cơ Bản để nâng cấp.</t>
+          <t>Khi Phục Hồi đạt đến một cột mốc nhất định, hãy đến Trại Cơ Bản để nâng cấp nó.</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr"/>
@@ -11615,7 +11615,7 @@
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>Khi Restoration đạt đến một mốc nhất định, hãy đến Trại Cơ Bản để nâng cấp.</t>
+          <t>Khi Phục Hồi đạt đến một cột mốc nhất định, hãy đến Trại Cơ Bản để nâng cấp nó.</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr"/>
@@ -11681,7 +11681,7 @@
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>Khi Restoration đạt đến một mốc nhất định, hãy đến Trại Cơ Bản để nâng cấp.</t>
+          <t>Khi Phục Hồi đạt đến một cột mốc nhất định, hãy đến Trại Cơ Bản để nâng cấp nó.</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr"/>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>Hiển thị tiến trình nâng cấp Trại Cơ bản lên cấp tiếp theo.</t>
+          <t>Màn hình này hiển thị tiến độ nâng cấp Trại Cơ Bản lên cấp tiếp theo.</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr"/>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>Hiển thị tiến trình nâng cấp Trại Cơ bản lên cấp tiếp theo.</t>
+          <t>Màn hình này hiển thị tiến độ nâng cấp Trại Cơ Bản lên cấp tiếp theo.</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr"/>
@@ -11879,7 +11879,7 @@
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>Hiển thị tiến trình nâng cấp Trại Cơ bản lên cấp tiếp theo.</t>
+          <t>Màn hình này hiển thị tiến độ nâng cấp Trại Cơ Bản lên cấp tiếp theo.</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr"/>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để đến Trại Cơ Bản.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để đến Trại Chính.</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr"/>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để đến Trại Cơ Bản.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để đến Trại Chính.</t>
         </is>
       </c>
       <c r="N175" s="2" t="inlineStr"/>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để đến Trại Cơ Bản.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để đến Trại Chính.</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr"/>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để mở nhanh giao diện Survey và tiếp tục khảo sát Dimmr Plains.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để mở nhanh giao diện Khảo sát và tiếp tục tiến trình khảo sát Dimmr Plains</t>
         </is>
       </c>
       <c r="N177" s="2" t="inlineStr"/>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để mở nhanh giao diện Survey và tiếp tục khảo sát Dimmr Plains.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để mở nhanh giao diện Khảo sát và tiếp tục tiến trình khảo sát Dimmr Plains</t>
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr"/>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để mở nhanh giao diện Survey và tiếp tục khảo sát Dimmr Plains.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để mở nhanh giao diện Khảo sát và tiếp tục tiến trình khảo sát Dimmr Plains</t>
         </is>
       </c>
       <c r="N179" s="2" t="inlineStr"/>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>Nhiệm vụ quan trọng khác trong chương hiện tại.</t>
+          <t>Những nhiệm vụ quan trọng khác trong chương hiện tại.</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>Nhiệm vụ quan trọng khác trong chương hiện tại.</t>
+          <t>Những nhiệm vụ quan trọng khác trong chương hiện tại.</t>
         </is>
       </c>
       <c r="N181" s="2" t="inlineStr"/>
@@ -12473,7 +12473,7 @@
       </c>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>Nhiệm vụ quan trọng khác trong chương hiện tại.</t>
+          <t>Những nhiệm vụ quan trọng khác trong chương hiện tại.</t>
         </is>
       </c>
       <c r="N182" s="2" t="inlineStr"/>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra Nhiệm Vụ Modding để nhận Điểm Modding Hàng Không.</t>
+          <t>Kiểm tra Nhiệm Vụ Chỉnh Sửa để nhận Điểm Chỉnh Sửa Hàng Không.</t>
         </is>
       </c>
       <c r="N183" s="2" t="inlineStr"/>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra Nhiệm Vụ Modding để nhận Điểm Modding Hàng Không.</t>
+          <t>Kiểm tra Nhiệm Vụ Chỉnh Sửa để nhận Điểm Chỉnh Sửa Hàng Không.</t>
         </is>
       </c>
       <c r="N184" s="2" t="inlineStr"/>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra Nhiệm Vụ Modding để nhận Điểm Modding Hàng Không.</t>
+          <t>Kiểm tra Nhiệm Vụ Chỉnh Sửa để nhận Điểm Chỉnh Sửa Hàng Không.</t>
         </is>
       </c>
       <c r="N185" s="2" t="inlineStr"/>
@@ -12737,7 +12737,7 @@
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>Mở tab Aerial Tactics để nhận Points Điều Chỉnh Trên Không.</t>
+          <t>Mở tab Chiến Thuật Trên Không để nhận Điểm Nâng Cấp Hàng Không.</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr"/>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>Mở tab Aerial Tactics để nhận Points Điều Chỉnh Trên Không.</t>
+          <t>Mở tab Chiến Thuật Trên Không để nhận Điểm Nâng Cấp Hàng Không.</t>
         </is>
       </c>
       <c r="N187" s="2" t="inlineStr"/>
@@ -12869,7 +12869,7 @@
       </c>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>Mở tab Aerial Tactics để nhận Points Điều Chỉnh Trên Không.</t>
+          <t>Mở tab Chiến Thuật Trên Không để nhận Điểm Nâng Cấp Hàng Không.</t>
         </is>
       </c>
       <c r="N188" s="2" t="inlineStr"/>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>Nhận Points Điều Chỉnh Hàng Không.</t>
+          <t>Nhận Điểm Điều Chỉnh Hàng Không.</t>
         </is>
       </c>
       <c r="N189" s="2" t="inlineStr"/>
@@ -13001,7 +13001,7 @@
       </c>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>Nhận Points Điều Chỉnh Hàng Không.</t>
+          <t>Nhận Điểm Điều Chỉnh Hàng Không.</t>
         </is>
       </c>
       <c r="N190" s="2" t="inlineStr"/>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>Nhận Points Điều Chỉnh Hàng Không.</t>
+          <t>Nhận Điểm Điều Chỉnh Hàng Không.</t>
         </is>
       </c>
       <c r="N191" s="2" t="inlineStr"/>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>Đến Mô-đun Mở Rộng Aerial Tactics để cải thiện hiệu suất xe máy.</t>
+          <t>Đến Mô-đun Mở Rộng Chiến Thuật Trên Không để cải thiện hiệu suất xe máy.</t>
         </is>
       </c>
       <c r="N192" s="2" t="inlineStr"/>
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>Đến Mô-đun Mở Rộng Aerial Tactics để cải thiện hiệu suất xe máy.</t>
+          <t>Đến Mô-đun Mở Rộng Chiến Thuật Trên Không để cải thiện hiệu suất xe máy.</t>
         </is>
       </c>
       <c r="N193" s="2" t="inlineStr"/>
@@ -13265,7 +13265,7 @@
       </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>Đến Mô-đun Mở Rộng Aerial Tactics để cải thiện hiệu suất xe máy.</t>
+          <t>Đến Mô-đun Mở Rộng Chiến Thuật Trên Không để cải thiện hiệu suất xe máy.</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr"/>
@@ -13331,7 +13331,7 @@
       </c>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>Xem Mô-đun Mở Rộng Chiến Thuật Hàng Không.</t>
+          <t>Xem Mô-đun Mở Rộng Chiến Thuật Trên Không.</t>
         </is>
       </c>
       <c r="N195" s="2" t="inlineStr"/>
@@ -13397,7 +13397,7 @@
       </c>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>Xem Mô-đun Mở Rộng Chiến Thuật Hàng Không.</t>
+          <t>Xem Mô-đun Mở Rộng Chiến Thuật Trên Không.</t>
         </is>
       </c>
       <c r="N196" s="2" t="inlineStr"/>
@@ -13463,7 +13463,7 @@
       </c>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>Xem Mô-đun Mở Rộng Chiến Thuật Hàng Không.</t>
+          <t>Xem Mô-đun Mở Rộng Chiến Thuật Trên Không.</t>
         </is>
       </c>
       <c r="N197" s="2" t="inlineStr"/>
@@ -13529,7 +13529,7 @@
       </c>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>Nâng cấp Nhảy Tích Lũy để mở khóa khả năng nhảy tích lũy.</t>
+          <t>Nâng cấp Bật Nhảy Tích Năng để mở khóa khả năng nhảy tích năng.</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr"/>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>Nâng cấp Nhảy Tích Lũy để mở khóa khả năng nhảy tích lũy.</t>
+          <t>Nâng cấp Bật Nhảy Tích Năng để mở khóa khả năng nhảy tích năng.</t>
         </is>
       </c>
       <c r="N199" s="2" t="inlineStr"/>
@@ -13661,7 +13661,7 @@
       </c>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>Nâng cấp Nhảy Tích Lũy để mở khóa khả năng nhảy tích lũy.</t>
+          <t>Nâng cấp Bật Nhảy Tích Năng để mở khóa khả năng nhảy tích năng.</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr"/>
@@ -13727,7 +13727,7 @@
       </c>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để mở khóa Mô-đun Mở Rộng Nhảy Tích Lũy.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để mở khóa Mô-đun Mở Rộng Nhảy Tích Năng.</t>
         </is>
       </c>
       <c r="N201" s="2" t="inlineStr"/>
@@ -13793,7 +13793,7 @@
       </c>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để mở khóa Mô-đun Mở Rộng Nhảy Tích Lũy.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để mở khóa Mô-đun Mở Rộng Nhảy Tích Năng.</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr"/>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để mở khóa Mô-đun Mở Rộng Nhảy Tích Lũy.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để mở khóa Mô-đun Mở Rộng Nhảy Tích Năng.</t>
         </is>
       </c>
       <c r="N203" s="2" t="inlineStr"/>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>Return menu chính để nâng cấp Persona Pinball của bạn.</t>
+          <t>Quay về menu chính để nâng cấp Pinball Nhân Cách</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr"/>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>Nhấn {0} để quay về menu chính và nâng cấp Persona Pinballs của bạn.</t>
+          <t>Nhấn {0} để quay lại menu chính và nâng cấp Persona Pinball của cậu.</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr"/>
@@ -14057,7 +14057,7 @@
       </c>
       <c r="M206" s="2" t="inlineStr">
         <is>
-          <t>Return menu chính để nâng cấp Persona Pinball của bạn.</t>
+          <t>Quay về menu chính để nâng cấp Pinball Nhân Cách</t>
         </is>
       </c>
       <c r="N206" s="2" t="inlineStr"/>
@@ -14123,7 +14123,7 @@
       </c>
       <c r="M207" s="2" t="inlineStr">
         <is>
-          <t>Bạn cũng có thể chọn các Persona Pinball khác để nhanh chóng tạo đội hình.</t>
+          <t>Cậu cũng có thể chọn các Viên Bi Nhân Cách khác để nhanh chóng xếp đội hình.</t>
         </is>
       </c>
       <c r="N207" s="2" t="inlineStr">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="M208" s="2" t="inlineStr">
         <is>
-          <t>Bạn cũng có thể chọn các Persona Pinball khác để nhanh chóng tạo đội hình.</t>
+          <t>Cậu cũng có thể chọn các Viên Bi Nhân Cách khác để nhanh chóng xếp đội hình.</t>
         </is>
       </c>
       <c r="N208" s="2" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="M209" s="2" t="inlineStr">
         <is>
-          <t>Bạn cũng có thể chọn các Persona Pinball khác để nhanh chóng tạo đội hình.</t>
+          <t>Cậu cũng có thể chọn các Viên Bi Nhân Cách khác để nhanh chóng xếp đội hình.</t>
         </is>
       </c>
       <c r="N209" s="2" t="inlineStr">
@@ -14333,7 +14333,7 @@
       </c>
       <c r="M210" s="2" t="inlineStr">
         <is>
-          <t>Bãi Tập Huấn Luyện Pioneer - Đối thủ tinh nhuệ</t>
+          <t>Khu Huấn Luyện Tinh Anh - Rover</t>
         </is>
       </c>
       <c r="N210" s="2" t="inlineStr"/>
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M211" s="2" t="inlineStr">
         <is>
-          <t>Bãi Tập Huấn Luyện Pioneer - Bù nhìn</t>
+          <t>Khu Huấn Luyện Tiên Phong - Bia Tập</t>
         </is>
       </c>
       <c r="N211" s="2" t="inlineStr"/>
@@ -14465,7 +14465,7 @@
       </c>
       <c r="M212" s="2" t="inlineStr">
         <is>
-          <t>Bãi Tập Huấn Luyện Pioneer - Tay sai</t>
+          <t>Khu Huấn Luyện Tinh Anh - Tay Chân</t>
         </is>
       </c>
       <c r="N212" s="2" t="inlineStr"/>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="M213" s="2" t="inlineStr">
         <is>
-          <t>Một đối thủ mạnh sẽ xuất hiện tại Khu Huấn Luyện này.</t>
+          <t>Một đối thủ mạnh sắp xuất hiện tại Khu Huấn Luyện này.</t>
         </is>
       </c>
       <c r="N213" s="2" t="inlineStr"/>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="M215" s="2" t="inlineStr">
         <is>
-          <t>Sẽ có nhiều đợt kẻ địch xuất hiện tại Khu Huấn Luyện này.</t>
+          <t>Nhiều đợt kẻ địch sẽ xuất hiện tại Khu Huấn Luyện này.</t>
         </is>
       </c>
       <c r="N215" s="2" t="inlineStr"/>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="M216" s="2" t="inlineStr">
         <is>
-          <t>Ba môi trường chiến đấu khác nhau được thiết lập tại Pioneer Training Ground để người chơi thử sức.</t>
+          <t>Ba môi trường chiến đấu khác nhau đã được thiết lập tại Khu Huấn Luyện Tiên Phong để người chơi thử sức.</t>
         </is>
       </c>
       <c r="N216" s="2" t="inlineStr"/>
@@ -14795,7 +14795,7 @@
       </c>
       <c r="M217" s="2" t="inlineStr">
         <is>
-          <t>Sẽ có nhiều đợt kẻ địch xuất hiện tại Khu Huấn Luyện này.</t>
+          <t>Nhiều đợt kẻ địch sẽ xuất hiện tại Khu Huấn Luyện này.</t>
         </is>
       </c>
       <c r="N217" s="2" t="inlineStr"/>
@@ -14861,7 +14861,7 @@
       </c>
       <c r="M218" s="2" t="inlineStr">
         <is>
-          <t>Khu Huấn Luyện Special Pioneer</t>
+          <t>Khu Huấn Luyện Đặc Biệt Tiên Phong</t>
         </is>
       </c>
       <c r="N218" s="2" t="inlineStr"/>
@@ -14927,7 +14927,7 @@
       </c>
       <c r="M219" s="2" t="inlineStr">
         <is>
-          <t>Nhận thưởng từ Polmes sau khi tìm thấy Missing Namipons.</t>
+          <t>Nhận phần thưởng từ Polmes sau khi tìm thấy Missing Namipons.</t>
         </is>
       </c>
       <c r="N219" s="2" t="inlineStr"/>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="M220" s="2" t="inlineStr">
         <is>
-          <t>Mua các loại Hộp Ngẫu Nhiên Hình Dán khác nhau từ Nhân Viên Bán Hàng.</t>
+          <t>Mua các loại Hộp Ngẫu Nhiên Hình Dán từ Nhà Vô Địch Bán Hàng.</t>
         </is>
       </c>
       <c r="N220" s="2" t="inlineStr"/>
@@ -15059,7 +15059,7 @@
       </c>
       <c r="M221" s="2" t="inlineStr">
         <is>
-          <t>Bộ sưu tập sẽ hiển thị các vật phẩm Legendary thu thập được.</t>
+          <t>Phòng Trưng bày sẽ hiển thị những vật phẩm huyền thoại mà các ngươi mang về.</t>
         </is>
       </c>
       <c r="N221" s="2" t="inlineStr"/>
@@ -15125,7 +15125,7 @@
       </c>
       <c r="M222" s="2" t="inlineStr">
         <is>
-          <t>Chỉnh đội hình Resonator trong Warehouse.</t>
+          <t>Chỉnh sửa đội hình Resonator trong Kho chứa</t>
         </is>
       </c>
       <c r="N222" s="2" t="inlineStr"/>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="M223" s="2" t="inlineStr">
         <is>
-          <t>Có thể xây dựng lại</t>
+          <t>Có thể tái xây dựng</t>
         </is>
       </c>
       <c r="N223" s="2" t="inlineStr"/>
@@ -15999,7 +15999,7 @@
       </c>
       <c r="M235" s="2" t="inlineStr">
         <is>
-          <t>Thanh Cảm Xúc</t>
+          <t>Thang Đo Cảm Xúc</t>
         </is>
       </c>
       <c r="N235" s="2" t="inlineStr">
@@ -16069,7 +16069,7 @@
       </c>
       <c r="M236" s="2" t="inlineStr">
         <is>
-          <t>Máy ảnh</t>
+          <t>Máy quay</t>
         </is>
       </c>
       <c r="N236" s="2" t="inlineStr"/>
@@ -16135,7 +16135,7 @@
       </c>
       <c r="M237" s="2" t="inlineStr">
         <is>
-          <t>Lahai-Roi: Hóa Thú</t>
+          <t>Lahai-Roi: Trở Thành Ác Thú</t>
         </is>
       </c>
       <c r="N237" s="2" t="inlineStr"/>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="M238" s="2" t="inlineStr">
         <is>
-          <t>Dawn Cơ Khí</t>
+          <t>Bình Minh Cơ Giới</t>
         </is>
       </c>
       <c r="N238" s="2" t="inlineStr"/>
@@ -16333,7 +16333,7 @@
       </c>
       <c r="M240" s="2" t="inlineStr">
         <is>
-          <t>Vũ điệu Diva</t>
+          <t>Điệu Nhảy Diva</t>
         </is>
       </c>
       <c r="N240" s="2" t="inlineStr"/>
@@ -16465,7 +16465,7 @@
       </c>
       <c r="M242" s="2" t="inlineStr">
         <is>
-          <t>Tiền không ngủ bao giờ</t>
+          <t>Tiền Không Ngủ</t>
         </is>
       </c>
       <c r="N242" s="2" t="inlineStr"/>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="M243" s="2" t="inlineStr">
         <is>
-          <t>Với những biomech thoát khỏi lồng giam, trở thành những con thú thực thụ luôn là khát khao sâu thẳm nhất của chúng. Đáng tiếc là chúng được tạo ra với quá nhiều nhân tính và quá ít sự man rợ.</t>
+          <t>Với những cỗ máy sinh học đã thoát khỏi lồng giam, trở thành những con thú thực thụ luôn là khát khao sâu thẳm nhất của chúng. Đáng tiếc thay, chúng được tạo ra với quá nhiều nhân tính và quá ít bản năng hoang dã.</t>
         </is>
       </c>
       <c r="N243" s="2" t="inlineStr"/>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="M244" s="2" t="inlineStr">
         <is>
-          <t>Những cỗ máy sinh học đã cố gắng truyền đạt "trí tuệ" lưu trữ trong cơ sở dữ liệu của chúng cho các sinh vật khác, nhưng sự thấu hiểu lẫn nhau chưa bao giờ khả thi.</t>
+          <t>Những cỗ máy sinh học cố truyền đạt "trí tuệ" lưu trong cơ sở dữ liệu của chúng cho các sinh vật khác, nhưng sự thấu hiểu lẫn nhau chẳng bao giờ có thể xảy ra.</t>
         </is>
       </c>
       <c r="N244" s="2" t="inlineStr"/>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="M245" s="2" t="inlineStr">
         <is>
-          <t>Đây là một kỷ nguyên của máy móc, và là một kỷ nguyên vĩ đại.</t>
+          <t>Đây là thời đại của máy móc, và là một thời đại vĩ đại.</t>
         </is>
       </c>
       <c r="N245" s="2" t="inlineStr"/>
@@ -16729,7 +16729,7 @@
       </c>
       <c r="M246" s="2" t="inlineStr">
         <is>
-          <t>Một số nhà nghiên cứu tin rằng biomech có khả năng thưởng thức "nghệ thuật." Tuy nhiên, hầu hết khẳng định đó chỉ là ảo giác do thuật toán.</t>
+          <t>Một số nhà nghiên cứu tin rằng biomech có khả năng thưởng thức "nghệ thuật". Tuy nhiên, hầu hết đều khẳng định đó chỉ là ảo giác do thuật toán tạo ra.</t>
         </is>
       </c>
       <c r="N246" s="2" t="inlineStr"/>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="M247" s="2" t="inlineStr">
         <is>
-          <t>Giờ đây, khi tự do phải đánh đổi bằng xương máu đang bị đe dọa, các biomech đã sẵn sàng cho một trận chiến tuyệt vọng.</t>
+          <t>Giờ đây, khi tự do phải đánh đổi bằng xương máu đang bị đe dọa, những cỗ máy sinh học đã sẵn sàng cho một trận chiến tuyệt vọng.</t>
         </is>
       </c>
       <c r="N247" s="2" t="inlineStr"/>
@@ -16931,11 +16931,11 @@
       </c>
       <c r="M249" s="2" t="inlineStr">
         <is>
-          <t>Riot Blades
-Cấp 0: &lt;color=Highlight&gt;Concerto Regen&lt;/color&gt; tăng 50%. Không thể bị hạ gục trong thử thách.
-Cấp 1: Khi gây &lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt; hoặc gây sát thương bằng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;, bắn Riot Blades về phía kẻ địch gần đó, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. Cooldown: 4 giây.
-Cấp 2: Cooldown của &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; giảm 50%. Riot Blades tồn tại lâu hơn và có thể di chuyển quỹ đạo trong khoảng cách ngắn, Cooldown giảm 2 giây.
-Cấp 3: &lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt; được khuếch đại 200%. Mỗi kẻ địch trúng Riot Blades sẽ phục hồi 5 Resonance Energy.</t>
+          <t>Lưỡi Kiếm Bạo Loạn
+Cấp 0: &lt;color=Highlight&gt;Hồi Phục Năng Lượng&lt;/color&gt; tăng 50%. Không thể bị hạ gục trong thử thách.
+Cấp 1: Khi gây &lt;color=Highlight&gt;Sát Thương Resonance Liberation&lt;/color&gt; hoặc gây DMG bằng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;, bắn Lưỡi Kiếm Bạo Loạn về phía kẻ địch gần đó, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;. Thời gian hồi: 4 giây.
+Cấp 2: Thời gian hồi chiêu &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; giảm 50%. Lưỡi Kiếm Bạo Loạn tồn tại lâu hơn và có thể di chuyển quỹ đạo trong khoảng cách ngắn, Thời gian hồi chiêu giảm 2 giây.
+Cấp 3: &lt;color=Highlight&gt;Sát Thương Resonance Liberation&lt;/color&gt; được khuếch đại 200%. Mỗi kẻ địch trúng Lưỡi Kiếm Bạo Loạn sẽ hồi 5 Resonance Energy.</t>
         </is>
       </c>
       <c r="N249" s="2" t="inlineStr"/>
@@ -17005,11 +17005,11 @@
       </c>
       <c r="M250" s="2" t="inlineStr">
         <is>
-          <t>Mind Shock
-Lv. 0: Khi &lt;color=Highlight&gt;ở trên không&lt;/color&gt;, Crit. DMG tăng 100%. Hiệu ứng mất đi sau 2 giây khi hạ cánh. Không thể bị hạ gục trong thử thách.
-Lv. 1: Khi &lt;color=Highlight&gt;ở trên không&lt;/color&gt;, cứ 4 đòn đánh sẽ tạo ra 1 Data Core, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Lv. 2: Số đòn đánh để tạo Data Core giảm còn 2. Mỗi lần tạo sẽ tách thành 3 lõi, tăng bán kính sát thương và khiến kẻ địch chịu thêm 60% sát thương khuếch đại.
-Lv. 3: Data Core kích hoạt Mind Shock, gây sát thương bổ sung.</t>
+          <t>Sốc Tâm Thức
+Cấp 0: Khi &lt;color=Highlight&gt;ở trên không&lt;/color&gt;, Crit. DMG tăng 100%. Hiệu ứng mất đi sau 2 giây khi hạ cánh. Không thể bị hạ gục trong thử thách.
+Cấp 1: Khi &lt;color=Highlight&gt;ở trên không&lt;/color&gt;, mỗi 4 đòn đánh tạo ra một Lõi Dữ Liệu, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Cấp 2: Số đòn đánh để tạo Lõi Dữ Liệu giảm xuống còn 2. Mỗi lần tạo sẽ tách thành 3 lõi, tăng bán kính DMG và khiến kẻ địch chịu thêm 60% Sát Thương Khuếch Đại.
+Cấp 3: Lõi Dữ Liệu kích hoạt Sốc Tâm Thức, gây thêm DMG.</t>
         </is>
       </c>
       <c r="N250" s="2" t="inlineStr"/>
@@ -17079,11 +17079,11 @@
       </c>
       <c r="M251" s="2" t="inlineStr">
         <is>
-          <t>Impulse Tide
-Cấp 0: Gây &lt;color=Highlight&gt;DMG Heavy Attack&lt;/color&gt; hoặc gây sát thương bằng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; sẽ nhận 60% DMG Bonus cho tất cả thuộc tính. Không thể bị hạ gục trong thử thách.
-Cấp 1: Gây &lt;color=Highlight&gt;DMG Heavy Attack&lt;/color&gt; hoặc gây sát thương bằng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; sẽ tạo ra Impulse Tide hút mục tiêu gần đó và gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. CD: 5 giây.
-Cấp 2: Thời gian Cooldown của Impulse Tide giảm 2 giây. Mục tiêu bị ảnh hưởng nhận sát thương tăng 60%.
-Cấp 3: Impulse Tide giải phóng một làn sóng xung kích, gây sát thương bổ sung.</t>
+          <t>Sóng Xung Kích
+Cấp 0: Gây &lt;color=Highlight&gt;Sát Thương Đòn Heavy Attack&lt;/color&gt; hoặc gây DMG bằng &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; sẽ nhận thêm 60% Tăng Sát Thương Toàn Thuộc Tính. Không thể bị hạ gục trong thử thách.
+Cấp 1: Gây &lt;color=Highlight&gt;Sát Thương Đòn Heavy Attack&lt;/color&gt; hoặc gây DMG bằng &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; sẽ tạo ra Sóng Xung Kích hút mục tiêu xung quanh và gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. Thời gian hồi: 5 giây.
+Cấp 2: Thời gian hồi chiêu của Sóng Xung Kích giảm 2 giây. Mục tiêu bị ảnh hưởng nhận Sát Thương Khuếch Đại thêm 60%.
+Cấp 3: Sóng Xung Kích giải phóng sóng chấn động, gây thêm DMG.</t>
         </is>
       </c>
       <c r="N251" s="2" t="inlineStr"/>
@@ -17153,11 +17153,11 @@
       </c>
       <c r="M252" s="2" t="inlineStr">
         <is>
-          <t>Hypnotic Chant
-Cấp 0: Tất cả DMG từ &lt;color=Highlight&gt;Negative Status&lt;/color&gt; được Khuếch Đại thêm 100%. Không thể bị hạ gục trong thử thách.
-Cấp 1: Đánh bại mục tiêu đang chịu &lt;color=Highlight&gt;Negative Statuses&lt;/color&gt; sẽ để lại một Ceaseless Chant, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; mỗi giây lên kẻ địch gần đó.
-Cấp 2: DMG gây lên kẻ địch đang chịu &lt;color=Highlight&gt;Negative Statuses&lt;/color&gt; được Khuếch Đại thêm 100%. Đánh bại kẻ địch như vậy sẽ áp dụng 1 tầng &lt;color=Highlight&gt;Negative Status&lt;/color&gt; tương tự lên kẻ địch gần đó. DMG của Ceaseless Chant tăng thêm 100%.
-Cấp 3: DMG của Ceaseless Chant tiếp tục tăng. Nó phát nổ mỗi 4 giây, gây thêm sát thương và tăng 1 tầng &lt;color=Highlight&gt;Negative Status&lt;/color&gt; cho kẻ địch bị ảnh hưởng.</t>
+          <t>Thánh Ca Thôi Miên
+Cấp 0: Tất cả &lt;color=Highlight&gt;Sát Thương Trạng Thái Tiêu Cực&lt;/color&gt; được Khuếch Đại thêm 100%. Không thể bị hạ gục trong thử thách.
+Cấp 1: Khi đánh bại mục tiêu chịu &lt;color=Highlight&gt;Trạng Thái Tiêu Cực&lt;/color&gt;, sẽ để lại một Bản Thánh Ca Bất Tận, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; mỗi giây lên các mục tiêu xung quanh.
+Cấp 2: DMG gây ra lên kẻ địch chịu &lt;color=Highlight&gt;Trạng Thái Tiêu Cực&lt;/color&gt; được Khuếch Đại thêm 100%. Khi đánh bại chúng, sẽ áp dụng 1 tầng &lt;color=Highlight&gt;Trạng Thái Tiêu Cực&lt;/color&gt; tương tự lên các mục tiêu xung quanh. DMG Bản Thánh Ca Bất Tận tăng thêm 100%.
+Cấp 3: DMG Bản Thánh Ca Bất Tận tiếp tục tăng. Mỗi 4 giây, nó sẽ phát nổ, gây thêm DMG và tăng 1 tầng &lt;color=Highlight&gt;Trạng Thái Tiêu Cực&lt;/color&gt; cho các mục tiêu bị ảnh hưởng.</t>
         </is>
       </c>
       <c r="N252" s="2" t="inlineStr"/>
@@ -17227,11 +17227,11 @@
       </c>
       <c r="M253" s="2" t="inlineStr">
         <is>
-          <t>Móng Piercing Claw
-Cấp 0: Dùng &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; tăng ATK 35%, cộng dồn tối đa 2 lần. Không thể bị hạ gục trong thử thách.
-Cấp 1: Dùng &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; phóng 6 Móng Piercing Claw gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Hiệu ứng này có Cooldown 3 giây.
-Cấp 2: Cooldown của &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; giảm 85%. Dùng Echo Skill tăng DMG của tất cả Resonators trong đội thêm 60% trong 5 giây.
-Cấp 3: Móng Piercing Claw quay trở lại sau khi phóng, gây thêm sát thương.</t>
+          <t>Vuốt Xuyên Thấu
+Cấp 0: Sử dụng &lt;color=Highlight&gt;Kỹ Năng Echo&lt;/color&gt; tăng ATK thêm 35%, có thể chồng chất tối đa 2 lần. Không thể bị hạ gục trong thử thách.
+Cấp 1: Sử dụng &lt;color=Highlight&gt;Kỹ Năng Echo&lt;/color&gt; phóng ra 6 Vuốt Xuyên Thấu gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;. Hiệu ứng này có Thời gian hồi chiêu 3 giây.
+Cấp 2: Thời gian hồi chiêu &lt;color=Highlight&gt;Kỹ Năng Echo&lt;/color&gt; giảm 85%. Sử dụng Kỹ Năng Echo sẽ khuếch đại DMG của tất cả Resonator trong đội thêm 60% trong 5 giây.
+Cấp 3: Vuốt Xuyên Thấu quay trở lại sau khi phóng, gây thêm DMG.</t>
         </is>
       </c>
       <c r="N253" s="2" t="inlineStr"/>
@@ -17301,11 +17301,11 @@
       </c>
       <c r="M254" s="2" t="inlineStr">
         <is>
-          <t>Tiến thoái lưỡng nan ngân sách
-Cấp 0: Tỷ lệ &lt;color=Highlight&gt;Tích lũy Lệch Nhịp&lt;/color&gt; tăng 300%. Không thể bị hạ gục trong thử thách.
-Cấp 1: Khi sử dụng &lt;color=Highlight&gt;Phá Nhịp&lt;/color&gt;, bắn Thiết Kế Chết Người vào kẻ địch gần đó, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Cấp 2: Sử dụng &lt;color=Highlight&gt;Phá Nhịp&lt;/color&gt; làm tăng &lt;color=Highlight&gt;Tăng Cường Phá Nhịp&lt;/color&gt; của tất cả Resonators trong đội lên 200. Thiết Kế Chết Người giờ có thể làm đình trệ kẻ địch và để lại 3 Lồng Budget, gây sát thương thêm.
-Cấp 3: Lồng Budget gây sát thương thêm khi hết hiệu lực.</t>
+          <t>Tiến Thoái Lưỡng Nan
+Cấp 0: &lt;color=Highlight&gt;Off-Tune Buildup Rate&lt;/color&gt; is increased by 300%. Cannot be downed during the challenge.
+Lv. 1: When casting &lt;color=Highlight&gt;Tune Break&lt;/color&gt;, fire Deadly Design toward nearby enemies, dealing &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
+Lv. 2: Casting &lt;color=Highlight&gt;Tune Break&lt;/color&gt; increases &lt;color=Highlight&gt;Tune Break Boost&lt;/color&gt; of all Resonators in the team by 200. Deadly Design can now stagnate enemies and leave behind 3 Budget Cages, dealing additional damage.
+Lv. 3: Budget Cages deal additional damage when they expire.</t>
         </is>
       </c>
       <c r="N254" s="2" t="inlineStr"/>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="M255" s="2" t="inlineStr">
         <is>
-          <t>Ảo mộng Sắc màu: Khởi Nguyên</t>
+          <t>Ảo Ảnh Sắc Màu: Khởi Nguyên</t>
         </is>
       </c>
       <c r="N255" s="2" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="M256" s="2" t="inlineStr">
         <is>
-          <t>Ảo mộng Sắc màu I</t>
+          <t>Ảo Ảnh Sắc Màu I</t>
         </is>
       </c>
       <c r="N256" s="2" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="M257" s="2" t="inlineStr">
         <is>
-          <t>Ảo mộng Sắc màu II</t>
+          <t>Ảo Ảnh Sắc Màu II</t>
         </is>
       </c>
       <c r="N257" s="2" t="inlineStr">
@@ -17581,7 +17581,7 @@
       </c>
       <c r="M258" s="2" t="inlineStr">
         <is>
-          <t>Ảo mộng Sắc màu III</t>
+          <t>Ảo Ảnh Sắc Màu III</t>
         </is>
       </c>
       <c r="N258" s="2" t="inlineStr">
@@ -17651,7 +17651,7 @@
       </c>
       <c r="M259" s="2" t="inlineStr">
         <is>
-          <t>Ảo mộng Sắc màu IV</t>
+          <t>Ảo Ảnh Sắc Màu IV</t>
         </is>
       </c>
       <c r="N259" s="2" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="M260" s="2" t="inlineStr">
         <is>
-          <t>Giữa mê cung giấc mơ này, liệu bạn sẽ tìm thấy sợi chỉ của người dệt nên nó ở đâu?</t>
+          <t>Trong mạng lưới giấc mơ sâu thẳm này, ngươi sẽ tìm thấy sợi chỉ của người dệt ở đâu?</t>
         </is>
       </c>
       <c r="N260" s="2" t="inlineStr"/>
@@ -17787,7 +17787,7 @@
       </c>
       <c r="M261" s="2" t="inlineStr">
         <is>
-          <t>Giữa mê cung giấc mơ này, liệu bạn sẽ tìm thấy sợi chỉ của người dệt nên nó ở đâu?</t>
+          <t>Trong mạng lưới giấc mơ sâu thẳm này, ngươi sẽ tìm thấy sợi chỉ của người dệt ở đâu?</t>
         </is>
       </c>
       <c r="N261" s="2" t="inlineStr"/>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="M262" s="2" t="inlineStr">
         <is>
-          <t>Giữa mê cung giấc mơ này, liệu bạn sẽ tìm thấy sợi chỉ của người dệt nên nó ở đâu?</t>
+          <t>Trong mạng lưới giấc mơ sâu thẳm này, ngươi sẽ tìm thấy sợi chỉ của người dệt ở đâu?</t>
         </is>
       </c>
       <c r="N262" s="2" t="inlineStr"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="M263" s="2" t="inlineStr">
         <is>
-          <t>Giữa mê cung giấc mơ này, liệu bạn sẽ tìm thấy sợi chỉ của người dệt nên nó ở đâu?</t>
+          <t>Trong mạng lưới giấc mơ sâu thẳm này, ngươi sẽ tìm thấy sợi chỉ của người dệt ở đâu?</t>
         </is>
       </c>
       <c r="N263" s="2" t="inlineStr"/>
@@ -17985,7 +17985,7 @@
       </c>
       <c r="M264" s="2" t="inlineStr">
         <is>
-          <t>Giữa mê cung giấc mơ này, liệu bạn sẽ tìm thấy sợi chỉ của người dệt nên nó ở đâu?</t>
+          <t>Trong mạng lưới giấc mơ sâu thẳm này, ngươi sẽ tìm thấy sợi chỉ của người dệt ở đâu?</t>
         </is>
       </c>
       <c r="N264" s="2" t="inlineStr"/>
@@ -18051,7 +18051,7 @@
       </c>
       <c r="M265" s="2" t="inlineStr">
         <is>
-          <t>Có thể khôi phục thêm Voidbane Eldertree</t>
+          <t>Có thể khôi phục thêm nhiều Cây Già Voidbane nữa</t>
         </is>
       </c>
       <c r="N265" s="2" t="inlineStr"/>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="M266" s="2" t="inlineStr">
         <is>
-          <t>Nâng Cấp Trại Cơ Bản</t>
+          <t>Nâng Cấp Trại Chính</t>
         </is>
       </c>
       <c r="N266" s="2" t="inlineStr"/>
@@ -18249,7 +18249,7 @@
       </c>
       <c r="M268" s="2" t="inlineStr">
         <is>
-          <t>Siren's Boneyard - Nửa Đầu</t>
+          <t>Nghĩa Địa Siran - Nửa Đầu</t>
         </is>
       </c>
       <c r="N268" s="2" t="inlineStr"/>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="M269" s="2" t="inlineStr">
         <is>
-          <t>Siren's Boneyard - Nửa Sau</t>
+          <t>Nghĩa Địa Siran - Nửa Sau</t>
         </is>
       </c>
       <c r="N269" s="2" t="inlineStr"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="M270" s="2" t="inlineStr">
         <is>
-          <t>Ruins Darkblight - First Half</t>
+          <t>Tàn Tích Hắc Ám - Nửa Đầu</t>
         </is>
       </c>
       <c r="N270" s="2" t="inlineStr"/>
@@ -18447,7 +18447,7 @@
       </c>
       <c r="M271" s="2" t="inlineStr">
         <is>
-          <t>Ruins Darkblight - Nửa Sau</t>
+          <t>Tàn Tích Hắc Ám - Nửa Sau</t>
         </is>
       </c>
       <c r="N271" s="2" t="inlineStr"/>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="M272" s="2" t="inlineStr">
         <is>
-          <t>Mistbound Lair - Nửa Đầu</t>
+          <t>Hang Sương Mù Trói Buộc - Nửa Đầu</t>
         </is>
       </c>
       <c r="N272" s="2" t="inlineStr"/>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M273" s="2" t="inlineStr">
         <is>
-          <t>Mistbound Lair - Nửa Sau</t>
+          <t>Hang Sương Mù Trói Buộc - Nửa Sau</t>
         </is>
       </c>
       <c r="N273" s="2" t="inlineStr"/>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="M274" s="2" t="inlineStr">
         <is>
-          <t>Weeping Walkway - Nửa Đầu</t>
+          <t>Hành Lang Than Khóc - Nửa Đầu</t>
         </is>
       </c>
       <c r="N274" s="2" t="inlineStr"/>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="M275" s="2" t="inlineStr">
         <is>
-          <t>Weeping Walkway - Nửa Sau</t>
+          <t>Hành Lang Than Khóc - Nửa Sau</t>
         </is>
       </c>
       <c r="N275" s="2" t="inlineStr"/>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="M276" s="2" t="inlineStr">
         <is>
-          <t>Starfall Expanse - Nửa Đầu</t>
+          <t>Vùng Đất Starfall - Nửa Đầu</t>
         </is>
       </c>
       <c r="N276" s="2" t="inlineStr"/>
@@ -18843,7 +18843,7 @@
       </c>
       <c r="M277" s="2" t="inlineStr">
         <is>
-          <t>Starfall Expanse - Nửa Sau</t>
+          <t>Vùng Trời Rơi Sao - Hồi Hai</t>
         </is>
       </c>
       <c r="N277" s="2" t="inlineStr"/>
@@ -18909,7 +18909,7 @@
       </c>
       <c r="M278" s="2" t="inlineStr">
         <is>
-          <t>Burial Bay - Nửa Đầu</t>
+          <t>Vịnh An Táng - Nửa Đầu</t>
         </is>
       </c>
       <c r="N278" s="2" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
       </c>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t>Burial Bay - Nửa Sau</t>
+          <t>Vịnh An Táng - Nửa Sau</t>
         </is>
       </c>
       <c r="N279" s="2" t="inlineStr"/>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="M280" s="2" t="inlineStr">
         <is>
-          <t>Doomstrand - Nửa Đầu</t>
+          <t>Dải Định Mệnh - Nửa Đầu</t>
         </is>
       </c>
       <c r="N280" s="2" t="inlineStr"/>
@@ -19107,7 +19107,7 @@
       </c>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>Doomstrand - Nửa Sau</t>
+          <t>Dải Định Mệnh - Nửa Sau</t>
         </is>
       </c>
       <c r="N281" s="2" t="inlineStr"/>
@@ -19173,7 +19173,7 @@
       </c>
       <c r="M282" s="2" t="inlineStr">
         <is>
-          <t>Whirlpool - Nửa Đầu</t>
+          <t>Vực Xoáy - Nửa Đầu</t>
         </is>
       </c>
       <c r="N282" s="2" t="inlineStr"/>
@@ -19239,7 +19239,7 @@
       </c>
       <c r="M283" s="2" t="inlineStr">
         <is>
-          <t>Xoáy Nước - Second Half</t>
+          <t>Vực Xoáy - Nửa Sau</t>
         </is>
       </c>
       <c r="N283" s="2" t="inlineStr"/>
@@ -19305,7 +19305,7 @@
       </c>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>Riptide - Nửa Đầu</t>
+          <t>Dòng Thủy Triều - Nửa Đầu</t>
         </is>
       </c>
       <c r="N284" s="2" t="inlineStr"/>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>Riptide - Nửa Sau</t>
+          <t>Dòng Thủy Triều - Nửa Sau</t>
         </is>
       </c>
       <c r="N285" s="2" t="inlineStr"/>
@@ -19437,7 +19437,7 @@
       </c>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>Tempest - Nửa Đầu</t>
+          <t>Bão Tố - Nửa Đầu</t>
         </is>
       </c>
       <c r="N286" s="2" t="inlineStr"/>
@@ -19503,7 +19503,7 @@
       </c>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t>Tempest - Hồi Hai</t>
+          <t>Bão Tố - Nửa Sau</t>
         </is>
       </c>
       <c r="N287" s="2" t="inlineStr"/>
@@ -19569,7 +19569,7 @@
       </c>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>Seabane - Nửa Đầu</t>
+          <t>Seabane - Nửa đầu</t>
         </is>
       </c>
       <c r="N288" s="2" t="inlineStr"/>
@@ -19635,7 +19635,7 @@
       </c>
       <c r="M289" s="2" t="inlineStr">
         <is>
-          <t>Seabane - Nửa Sau</t>
+          <t>Seabane - Nửa sau</t>
         </is>
       </c>
       <c r="N289" s="2" t="inlineStr"/>
@@ -19701,7 +19701,7 @@
       </c>
       <c r="M290" s="2" t="inlineStr">
         <is>
-          <t>Infinite Torrents - Nửa đầu</t>
+          <t>Hồng Thủy Vô Tận - Nửa Đầu</t>
         </is>
       </c>
       <c r="N290" s="2" t="inlineStr"/>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="M291" s="2" t="inlineStr">
         <is>
-          <t>Infinite Torrents - Nửa Sau</t>
+          <t>Hồng Thủy Vô Tận - Nửa Sau</t>
         </is>
       </c>
       <c r="N291" s="2" t="inlineStr"/>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="M292" s="2" t="inlineStr">
         <is>
-          <t>Khi tham gia Challenge, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N292" s="2" t="inlineStr"/>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="M293" s="2" t="inlineStr">
         <is>
-          <t>Khi vào Challenge, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N293" s="2" t="inlineStr"/>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="M294" s="2" t="inlineStr">
         <is>
-          <t>Khi tham gia Challenge, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N294" s="2" t="inlineStr"/>
@@ -20031,7 +20031,7 @@
       </c>
       <c r="M295" s="2" t="inlineStr">
         <is>
-          <t>Khi vào Challenge, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N295" s="2" t="inlineStr"/>
@@ -20097,7 +20097,7 @@
       </c>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t>Khi tham gia Challenge, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N296" s="2" t="inlineStr"/>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="M297" s="2" t="inlineStr">
         <is>
-          <t>Khi vào Challenge, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N297" s="2" t="inlineStr"/>
@@ -20229,7 +20229,7 @@
       </c>
       <c r="M298" s="2" t="inlineStr">
         <is>
-          <t>Khi tham gia Challenge, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N298" s="2" t="inlineStr"/>
@@ -20295,7 +20295,7 @@
       </c>
       <c r="M299" s="2" t="inlineStr">
         <is>
-          <t>Khi vào Challenge, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N299" s="2" t="inlineStr"/>
@@ -20361,7 +20361,7 @@
       </c>
       <c r="M300" s="2" t="inlineStr">
         <is>
-          <t>Khi tham gia Challenge, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N300" s="2" t="inlineStr"/>
@@ -20427,7 +20427,7 @@
       </c>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>Khi vào Challenge, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N301" s="2" t="inlineStr"/>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>Khi tham gia Challenge, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N302" s="2" t="inlineStr"/>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>Khi vào Challenge, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N303" s="2" t="inlineStr"/>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>Khi tham gia Challenge, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N304" s="2" t="inlineStr"/>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>Khi vào Challenge, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N305" s="2" t="inlineStr"/>
@@ -20757,7 +20757,7 @@
       </c>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>Khi tham gia Challenge, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N306" s="2" t="inlineStr"/>
@@ -20823,7 +20823,7 @@
       </c>
       <c r="M307" s="2" t="inlineStr">
         <is>
-          <t>Khi vào Challenge, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N307" s="2" t="inlineStr"/>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="M308" s="2" t="inlineStr">
         <is>
-          <t>Khi tham gia Challenge, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N308" s="2" t="inlineStr"/>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="M309" s="2" t="inlineStr">
         <is>
-          <t>Khi vào Challenge, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N309" s="2" t="inlineStr"/>
@@ -21021,7 +21021,7 @@
       </c>
       <c r="M310" s="2" t="inlineStr">
         <is>
-          <t>Khi tham gia Challenge, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N310" s="2" t="inlineStr"/>
@@ -21087,7 +21087,7 @@
       </c>
       <c r="M311" s="2" t="inlineStr">
         <is>
-          <t>Khi vào Challenge, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N311" s="2" t="inlineStr"/>
@@ -21153,7 +21153,7 @@
       </c>
       <c r="M312" s="2" t="inlineStr">
         <is>
-          <t>Khi tham gia Challenge, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N312" s="2" t="inlineStr"/>
@@ -21219,7 +21219,7 @@
       </c>
       <c r="M313" s="2" t="inlineStr">
         <is>
-          <t>Khi vào Challenge, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N313" s="2" t="inlineStr"/>
@@ -21285,7 +21285,7 @@
       </c>
       <c r="M314" s="2" t="inlineStr">
         <is>
-          <t>Khi tham gia Challenge, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Concerto Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N314" s="2" t="inlineStr"/>
@@ -21351,7 +21351,7 @@
       </c>
       <c r="M315" s="2" t="inlineStr">
         <is>
-          <t>Khi vào Challenge, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; sẽ được phục hồi về 100%</t>
+          <t>Khi tham gia Thử Thách, &lt;color=#ffb04a&gt;Resonance Energy&lt;/color&gt; được hồi phục về 100%.</t>
         </is>
       </c>
       <c r="N315" s="2" t="inlineStr"/>
@@ -21419,9 +21419,9 @@
       </c>
       <c r="M316" s="2" t="inlineStr">
         <is>
-          <t>Vùng đất rộng lớn và hoang vu này là nơi an nghỉ của vô số Pilgrim's Sail. Discord khổng lồ hình rồng không ngừng nuốt chửng các tần số xung quanh, và Remnant Clouds thu hút Discord tụ tập—đừng bao giờ lơ là khi đi qua hòn đảo bị bỏ hoang này.
-[Lưu ý]
-Resonators ở các độ cao khác nhau tại Solaris di chuyển với tốc độ khác nhau.</t>
+          <t>Vùng đất hoang vu, rộng lớn này là nơi an nghỉ của vô số Cánh Buồm Hành Hương. Tổ Tacet hình rồng khổng lồ không ngừng nuốt chửng các tần số xung quanh, còn Mây Tàn Tích lại thu hút thêm Tacet Discord về đây—đừng bao giờ lơ là cảnh giác khi đặt chân lên hòn đảo bị bỏ hoang này.
+[Ghi chú]
+Resonator ở các độ cao khác nhau trên Solaris di chuyển với tốc độ khác nhau.</t>
         </is>
       </c>
       <c r="N316" s="2" t="inlineStr"/>
@@ -21489,9 +21489,9 @@
       </c>
       <c r="M317" s="2" t="inlineStr">
         <is>
-          <t>Một kho tàng chứa đầy Echoes và bảo vật vô giá nổi lên trên mặt nước huyền ảo. Khi bay lượn trên cao, bạn có thể thấy mình như đang bơi trong biển mây trắng xóa.
-[Lưu ý]
-Resonators ở các độ cao khác nhau tại Solaris sẽ di chuyển với tốc độ khác nhau.</t>
+          <t>Một kho tàng vươn cao giữa làn nước huyền ảo, chứa đựng những Echo và hiện vật vô giá. Khi bay lướt qua, bạn có thể thấy mình như đang bơi trong biển mây trắng xóa.
+[Ghi chú]
+Resonator ở các độ cao khác nhau trên Solaris di chuyển với tốc độ khác nhau.</t>
         </is>
       </c>
       <c r="N317" s="2" t="inlineStr"/>
@@ -21559,9 +21559,9 @@
       </c>
       <c r="M318" s="2" t="inlineStr">
         <is>
-          <t>Trong làn gió lạnh, những khúc nhạc nhạt nhòa vang vọng trong đêm vĩnh hằng. Dưới ánh trăng và làn sương mù, một con đường dài dẫn đến nơi bí ẩn dường như đang mở ra trước mắt bạn.
+          <t>Trong làn gió lạnh giá, những khúc nhạc mờ ảo vẫn vương vấn trong đêm dài bất tận. Dưới ánh trăng và màn sương mỏng, một con đường bí ẩn như đang mở ra trước mắt cậu.
 [Ghi chú]
-Resonators ở các độ cao khác nhau tại Solaris di chuyển với tốc độ khác nhau.</t>
+Resonator ở các tầng khác nhau của Solaris di chuyển với tốc độ khác nhau.</t>
         </is>
       </c>
       <c r="N318" s="2" t="inlineStr"/>
@@ -21629,9 +21629,9 @@
       </c>
       <c r="M319" s="2" t="inlineStr">
         <is>
-          <t>Tháp cao chót vót đứng trên Thessaleo Fells như một con cá kiếm cô độc, từng tách khỏi đàn nhưng luôn sẵn sàng thống trị biển sâu. Nó không ngừng hút năng lượng từ biển mây, tạo nên một vương miện tội lỗi.
+          <t>Ngọn tháp sừng sững trên Thessaleo Fells như một con cá kiếm cô độc, từng tách khỏi đàn nhưng luôn sẵn sàng thống trị biển sâu. Nó không ngừng hút năng lượng từ biển mây, rèn nên một vương miện tội lỗi.
 [Ghi chú]
-Resonators ở các độ cao khác nhau trong Solaris chạy với tốc độ khác nhau.</t>
+Resonator ở các độ cao khác nhau trên Solaris sẽ di chuyển với tốc độ khác nhau.</t>
         </is>
       </c>
       <c r="N319" s="2" t="inlineStr"/>
@@ -21699,9 +21699,9 @@
       </c>
       <c r="M320" s="2" t="inlineStr">
         <is>
-          <t>Đi thuyền qua một hồ nước thanh bình ôm trọn bởi rừng cây rậm rạp, rồi vượt qua những dãy núi rộng lớn và hang động tối tăm để chứng kiến khung cảnh ẩn giấu ở cuối hành trình.
-[Lưu ý]
-Resonators có chiều cao khác nhau ở Solaris sẽ di chuyển với tốc độ khác nhau.</t>
+          <t>Hãy lướt trên mặt hồ yên bình ôm trọn rừng cây rậm rạp, rồi vượt qua những dãy núi hùng vĩ và hang động tối tăm để khám phá cảnh sắc ẩn giấu nơi cuối hành trình.
+[Ghi chú]
+Resonator ở các độ cao khác nhau trên Solaris di chuyển với tốc độ khác nhau.</t>
         </is>
       </c>
       <c r="N320" s="2" t="inlineStr"/>
@@ -21769,9 +21769,9 @@
       </c>
       <c r="M321" s="2" t="inlineStr">
         <is>
-          <t>Những Tacet Discord dữ dội lượn vòng trên bầu trời, trong khi tàn tích của những thân cây đổ nát vương vãi trên đường. Không khí nặng mùi bão tố đang đến gần. Chỉ khi vượt qua sấm chớp và gió giật, ngươi mới có thể đến được vùng đất bình yên.
-[Lưu ý]
-Resonators ở các độ cao khác nhau tại Solaris sẽ di chuyển với tốc độ khác nhau.</t>
+          <t>Những Tacet Discord hung dữ lượn vòng trên bầu trời, trong khi tàn tích của những thân cây đổ ngổn ngang trên đường. Không khí nặng mùi bão tố đang đến gần. Chỉ khi vượt qua được sấm chớp và gió giật, ngươi mới có thể đặt chân đến vùng đất bình yên.
+[Ghi chú]
+Resonator ở các độ cao khác nhau tại Solaris di chuyển với tốc độ khác nhau.</t>
         </is>
       </c>
       <c r="N321" s="2" t="inlineStr"/>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="M322" s="2" t="inlineStr">
         <is>
-          <t>Giữa đống tàn tích biển phủ sương mù, những cái bẫy ẩn dụ dỗ dã các nhà thám hiểm tiến sâu hơn. Tacet Discord tràn ngập nơi đây, sẵn sàng nuốt chửng bất kỳ kẻ tò mò nào đến quá gần.</t>
+          <t>Giữa những tàn tích biển phủ sương mù, những cái bẫy ẩn dụ mời gọi kẻ thám hiểm tiến sâu hơn. Tacet Discord tràn ngập nơi đây, sẵn sàng nuốt chửng bất kỳ kẻ tò mò nào dám bén mảng đến gần.</t>
         </is>
       </c>
       <c r="N322" s="2" t="inlineStr"/>
@@ -21904,8 +21904,8 @@
       </c>
       <c r="M323" s="2" t="inlineStr">
         <is>
-          <t>Sau khi bị hạ gục trong Trial Tai Họa, người thách đấu có thể tiêu hao 3 Mức Căng Thẳng để hồi sinh. Điều này cũng sẽ mang lại buff tương ứng.
-Lưu ý rằng việc tiêu hao Mức Căng Thẳng sẽ ảnh hưởng đến việc hoàn thành và kết quả cuối cùng của Mục Tiêu Trial.</t>
+          <t>Sau khi bị hạ gục trong Thử Thách Tai Họa, người thách đấu có thể tiêu hao 3 Mức Căng Thẳng để hồi sinh. Điều này cũng mang lại hiệu ứng tăng cường tương ứng.
+Lưu ý rằng việc tiêu hao Mức Căng Thẳng sẽ ảnh hưởng đến việc hoàn thành và kết quả cuối cùng của Mục Tiêu Thử Thách.</t>
         </is>
       </c>
       <c r="N323" s="2" t="inlineStr"/>
@@ -21971,7 +21971,7 @@
       </c>
       <c r="M324" s="2" t="inlineStr">
         <is>
-          <t>Sau khi bị hạ gục trong Thử Thách Khủng Hoảng, người thách đấu có thể hồi sinh mà không tiêu hao Stress Levels và nhận buff tương ứng.</t>
+          <t>Sau khi bị hạ gục trong Thử Thách Khủng Hoảng, người thách đấu có thể hồi sinh mà không tiêu hao Mức Căng Thẳng và nhận được hiệu ứng tăng cường tương ứng.</t>
         </is>
       </c>
       <c r="N324" s="2" t="inlineStr"/>
@@ -22717,7 +22717,7 @@
       </c>
       <c r="M335" s="2" t="inlineStr">
         <is>
-          <t>Lễ kỷ niệm Second Coming of Solaris lần thứ hai đang đến gần, nhưng rắc rối đã ập đến thế giới Cube! Ma vương bí ẩn Abbowser đã bắt cóc tất cả các Cube và thách thức Chiến Binh Black Cat huyền thoại. "Hãy bước vào thế giới chưa biết, đối mặt với tay sai của ta, giải cứu những người bạn bị mất tích và đối đầu với ta trong trận chiến cuối cùng! Nào, sẽ rất thú vị đấy!"</t>
+          <t>Lễ Kỷ Niệm Sự Trở Lại Của Solaris sắp đến, nhưng rắc rối đã ập đến Thế Giới Khối Lập Phương! Vua quỷ bí ẩn Abbowser đã bắt cóc tất cả các Khối Lập Phương và thách thức Chiến Binh Mèo Đen huyền thoại. "Hãy bước vào thế giới bí ẩn, đối đầu với tay sai của ta, giải cứu bạn bè bị mất tích, và đối mặt với ta trong trận quyết chiến cuối cùng! Nào, sẽ rất thú vị đấy!"</t>
         </is>
       </c>
       <c r="N335" s="2" t="inlineStr"/>
@@ -28465,7 +28465,7 @@
       </c>
       <c r="M421" s="2" t="inlineStr">
         <is>
-          <t>Kiểm Tra Phiên Bản</t>
+          <t>Kiểm tra Phiên Bản</t>
         </is>
       </c>
       <c r="N421" s="2" t="inlineStr"/>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="M423" s="2" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} bất cứ đâu để đóng</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} bất cứ đâu để đóng</t>
         </is>
       </c>
       <c r="N423" s="2" t="inlineStr"/>
@@ -28670,10 +28670,10 @@
       </c>
       <c r="M424" s="2" t="inlineStr">
         <is>
-          <t>Nhận các tăng cường sau:
-- Khi bắt đầu thử thách, Resonance Energy được phục hồi 100%, và RES toàn thuộc tính của kẻ địch giảm về 0.
-- Một số đòn tấn công của Resonators có thể phá vỡ Tunability của kẻ địch và tích lũy Off-Tune Level. Kẻ địch sẽ rơi vào trạng thái Mistune khi Off-Tune Level đầy. Trong thời gian này, Resonators có thể biến hình thành Kerasaur để tấn công kẻ địch, đặt lại Off-Tune Level khi trúng đòn.
-- Kẻ địch sẽ rơi vào Mistune ngay lập tức khi một số đòn tấn công của chúng bị phản đòn hoặc Dodge thành công. Trong thời gian này, Resonators có thể thực hiện Tune Break để tấn công kẻ địch mà không đặt lại Off-Tune Level.</t>
+          <t>Nhận các hiệu ứng tăng cường sau:
+- Khi bắt đầu thử thách, Resonance Energy sẽ hồi phục 100%, và Kháng toàn bộ thuộc tính của kẻ địch giảm xuống 0.
+- Một số đòn tấn công của Resonator có thể làm gián đoạn Khả Năng Điều Chỉnh của kẻ địch và tích lũy Mức Lệch Nhịp. Khi Mức Lệch Nhịp đầy, kẻ địch sẽ rơi vào trạng thái Lệch Nhịp. Trong thời gian này, Resonator có thể biến hình thành Kerasaur để tấn công, làm reset Mức Lệch Nhịp của kẻ địch khi trúng đòn.
+- Khi một số đòn tấn công của kẻ địch bị phản công hoặc né tránh thành công, chúng sẽ lập tức rơi vào trạng thái Lệch Nhịp. Lúc này, Resonator có thể thực hiện Phá Nhịp để tấn công mà không làm reset Mức Lệch Nhịp của kẻ địch.</t>
         </is>
       </c>
       <c r="N424" s="2" t="inlineStr"/>
@@ -28742,10 +28742,10 @@
       </c>
       <c r="M425" s="2" t="inlineStr">
         <is>
-          <t>Nhận các nâng cấp sau:
-- Khi bắt đầu thử thách, Resonance Energy được phục hồi 100%, và RES toàn thuộc tính của kẻ địch giảm về 0.
-- Một số đòn tấn công của Resonators có thể phá vỡ Tunability của kẻ địch và tích lũy Off-Tune Level. Khi Off-Tune Level đầy, kẻ địch sẽ rơi vào trạng thái Mistune. Trong thời gian này, Resonators có thể biến hình thành Kerasaur để tấn công kẻ địch, và mỗi lần trúng đòn sẽ reset Off-Tune Level.
-- Kẻ địch sẽ lập tức rơi vào Mistune khi một số đòn tấn công của chúng bị phản đòn hoặc Dodge thành công. Trong thời gian này, Resonators có thể thực hiện Tune Break để tấn công kẻ địch mà không reset Off-Tune Level.</t>
+          <t>Nhận các hiệu ứng tăng cường sau:
+- Khi bắt đầu thử thách, Resonance Energy được hồi phục 100%, và Kháng Tất Cả Thuộc Tính của kẻ địch giảm xuống 0.
+- Một số đòn tấn công của Resonator có thể làm gián đoạn Tần Số của kẻ địch và tích lũy Mức Độ Lệch Tần. Khi Mức Độ Lệch Tần đầy, kẻ địch sẽ rơi vào trạng thái Mistune. Trong thời gian này, Resonator có thể biến hình thành Kerasaur để tấn công kẻ địch, đặt lại Mức Độ Lệch Tần khi trúng đòn.
+- Kẻ địch sẽ lập tức rơi vào Mistune khi một số đòn tấn công của chúng bị phản đòn hoặc né thành công. Trong thời gian này, Resonator có thể thực hiện Tune Break để tấn công kẻ địch mà không đặt lại Mức Độ Lệch Tần.</t>
         </is>
       </c>
       <c r="N425" s="2" t="inlineStr"/>
@@ -28815,11 +28815,11 @@
       </c>
       <c r="M426" s="2" t="inlineStr">
         <is>
-          <t>Nhận các tăng cường sau:
-- Khi bắt đầu thử thách, Resonance Energy được phục hồi 100%, và RES toàn thuộc tính của kẻ địch giảm xuống 0.
-- Một số đòn tấn công của Resonators có thể làm gián đoạn Tunability của kẻ địch và tích lũy Off-Tune Level. Kẻ địch sẽ rơi vào trạng thái Mistune khi Off-Tune Level đầy. Trong thời gian này, Resonators có thể biến hình thành Kerasaur để tấn công kẻ địch, đặt lại Off-Tune Level khi trúng đòn.
-- Kẻ địch sẽ rơi vào Mistune ngay lập tức khi một số đòn tấn công của chúng bị phản đòn hoặc Dodge thành công. Trong thời gian này, Resonators có thể thực hiện Tune Break để tấn công kẻ địch mà không đặt lại Off-Tune Level.
-Spectro Frazzle DMG gây bởi Resonators trong đội tích lũy Off-Tune Level nhanh hơn 100%.</t>
+          <t>Nhận các hiệu ứng tăng cường sau:
+- Khi bắt đầu thử thách, Resonance Energy hồi phục 100%, và Kháng toàn bộ thuộc tính của kẻ địch giảm xuống 0.
+- Một số đòn tấn công của Resonator có thể làm gián đoạn Tần Số của kẻ địch và tích lũy Mức Lệch Tần. Khi Mức Lệch Tần đầy, kẻ địch sẽ rơi vào trạng thái Lệch Tần. Trong thời gian này, Resonator có thể biến hình thành Kerasaur để tấn công kẻ địch, và mỗi lần trúng đòn sẽ đặt lại Mức Lệch Tần.
+- Khi phản đòn hoặc Né thành công một số đòn tấn công của kẻ địch, chúng sẽ lập tức rơi vào trạng thái Lệch Tần. Trong thời gian này, Resonator có thể thực hiện Phá Tần để tấn công mà không làm đặt lại Mức Lệch Tần.
+Sát Thương Spectro Frazzle do Resonator trong đội gây ra sẽ tích lũy Mức Lệch Tần nhanh gấp đôi.</t>
         </is>
       </c>
       <c r="N426" s="2" t="inlineStr"/>
@@ -28889,11 +28889,11 @@
       </c>
       <c r="M427" s="2" t="inlineStr">
         <is>
-          <t>Nhận các tăng cường sau:
-- Khi bắt đầu thử thách, Resonance Energy được phục hồi 100%, và RES toàn thuộc tính của kẻ địch giảm xuống 0.
-- Một số đòn tấn công nhất định của Resonators có thể làm gián đoạn Tunability của kẻ địch và tích lũy Off-Tune Level. Kẻ địch sẽ rơi vào trạng thái Mistune khi Off-Tune Level đầy. Trong thời gian này, Resonators có thể biến hình thành Kerasaur để tấn công kẻ địch, đặt lại Off-Tune Level khi trúng đòn.
-- Kẻ địch sẽ rơi vào Mistune ngay lập tức khi một số đòn tấn công của chúng bị phản đòn hoặc Dodge thành công. Trong thời gian này, Resonators có thể thực hiện Tune Break để tấn công kẻ địch mà không đặt lại Off-Tune Level.
-Havoc Bane DMG gây ra bởi Resonators trong đội sẽ tích lũy Off-Tune Level nhiều hơn 100% trong 30 giây.</t>
+          <t>Nhận các hiệu ứng tăng cường sau:
+- Khi bắt đầu thử thách, Resonance Energy sẽ hồi phục 100%, và Kháng toàn bộ thuộc tính của kẻ địch giảm xuống 0.
+- Một số đòn tấn công của Resonator có thể làm gián đoạn Khả Năng Điều Chỉnh của kẻ địch và tích lũy Mức Lệch Nhịp. Khi Mức Lệch Nhịp đầy, kẻ địch sẽ rơi vào trạng thái Lệch Nhịp. Trong thời gian này, Resonator có thể biến hình thành Kerasaur để tấn công, làm reset Mức Lệch Nhịp của kẻ địch khi trúng đòn.
+- Khi một số đòn tấn công của kẻ địch bị phản công hoặc né tránh thành công, chúng sẽ lập tức rơi vào trạng thái Lệch Nhịp. Lúc này, Resonator có thể thực hiện Phá Nhịp để tấn công mà không làm reset Mức Lệch Nhịp của kẻ địch.
+DMG Havoc Bane gây ra bởi Resonator trong đội sẽ tích lũy Mức Lệch Nhịp nhiều hơn 100% trong 30 giây.</t>
         </is>
       </c>
       <c r="N427" s="2" t="inlineStr"/>
@@ -28963,11 +28963,11 @@
       </c>
       <c r="M428" s="2" t="inlineStr">
         <is>
-          <t>Nhận các tăng cường sau:
-- Khi bắt đầu thử thách, Resonance Energy được phục hồi 100%, và RES toàn thuộc tính của kẻ địch giảm xuống 0.
-- Một số đòn tấn công của Resonators có thể làm gián đoạn Tunability của kẻ địch và tích lũy Off-Tune Level. Kẻ địch sẽ rơi vào trạng thái Mistune khi Off-Tune Level đầy. Trong thời gian này, Resonators có thể biến hình thành Kerasaur để tấn công kẻ địch, đặt lại Off-Tune Level khi trúng đòn.
-- Kẻ địch sẽ rơi vào Mistune ngay lập tức khi một số đòn tấn công của chúng bị phản đòn hoặc Dodge thành công. Trong thời gian này, Resonators có thể thực hiện Tune Break để tấn công kẻ địch mà không đặt lại Off-Tune Level.
-Echo Skill DMG gây ra bởi Resonators trong đội tích lũy Off-Tune Level nhanh hơn 100%.</t>
+          <t>Nhận các hiệu ứng tăng cường sau:
+- Khi bắt đầu thử thách, Resonance Energy sẽ hồi phục 100%, và Kháng toàn bộ thuộc tính của kẻ địch giảm xuống 0.
+- Một số đòn tấn công của Resonator có thể làm gián đoạn Khả Năng Điều Chỉnh của kẻ địch và tích lũy Mức Lệch Nhịp. Khi Mức Lệch Nhịp đầy, kẻ địch sẽ rơi vào trạng thái Lệch Nhịp. Trong thời gian này, Resonator có thể biến hình thành Kerasaur để tấn công, làm reset Mức Lệch Nhịp của kẻ địch khi trúng đòn.
+- Khi một số đòn tấn công của kẻ địch bị phản công hoặc né tránh thành công, chúng sẽ lập tức rơi vào trạng thái Lệch Nhịp. Lúc này, Resonator có thể thực hiện Phá Nhịp để tấn công mà không làm reset Mức Lệch Nhịp của kẻ địch.
+DMG Kỹ Năng Echo gây ra bởi Resonator trong đội sẽ tích lũy Mức Lệch Nhịp nhiều hơn 100%.</t>
         </is>
       </c>
       <c r="N428" s="2" t="inlineStr"/>
@@ -29037,11 +29037,11 @@
       </c>
       <c r="M429" s="2" t="inlineStr">
         <is>
-          <t>Nhận các tăng cường sau:
-- Khi bắt đầu thử thách, Resonance Energy được phục hồi 100%, và RES toàn thuộc tính của kẻ địch giảm xuống 0.
-- Một số đòn tấn công của Resonators có thể phá vỡ Tunability của kẻ địch và tích lũy Off-Tune Level. Khi Off-Tune Level đầy, kẻ địch sẽ rơi vào trạng thái Mistune. Trong thời gian này, Resonators có thể biến hình thành Kerasaur để tấn công kẻ địch, và mỗi lần trúng đòn sẽ đặt lại Off-Tune Level.
-- Khi một số đòn tấn công của kẻ địch bị phản đòn hoặc Dodge thành công, kẻ địch sẽ lập tức rơi vào Mistune. Trong thời gian này, Resonators có thể thực hiện Tune Break để tấn công kẻ địch mà không đặt lại Off-Tune Level.
-DMG gây ra bởi Resonators trong đội có Shield sẽ tích lũy Off-Tune Level nhanh hơn 100%.</t>
+          <t>Nhận các hiệu ứng tăng cường sau:
+- Khi bắt đầu thử thách, Resonance Energy sẽ hồi phục 100%, và Kháng toàn bộ thuộc tính của kẻ địch giảm xuống 0.
+- Một số đòn tấn công của Resonator có thể làm gián đoạn Khả Năng Điều Chỉnh của kẻ địch và tích lũy Mức Lệch Nhịp. Khi Mức Lệch Nhịp đầy, kẻ địch sẽ rơi vào trạng thái Lệch Nhịp. Trong thời gian này, Resonator có thể biến hình thành Kerasaur để tấn công, làm reset Mức Lệch Nhịp của kẻ địch khi trúng đòn.
+- Khi một số đòn tấn công của kẻ địch bị phản công hoặc né tránh thành công, chúng sẽ lập tức rơi vào trạng thái Lệch Nhịp. Lúc này, Resonator có thể thực hiện Phá Nhịp để tấn công mà không làm reset Mức Lệch Nhịp của kẻ địch.
+DMG gây ra bởi Resonator trong đội có Khiên sẽ tích lũy Mức Lệch Nhịp nhiều hơn 100%.</t>
         </is>
       </c>
       <c r="N429" s="2" t="inlineStr"/>
@@ -29107,7 +29107,7 @@
       </c>
       <c r="M430" s="2" t="inlineStr">
         <is>
-          <t>Sử dụng Spacetrek Observatory để phát tín hiệu điều khiển, điều chỉnh Mảng Dự Báo Bầu Trời nhằm tạo ra thời tiết mô phỏng trên khắp Lahai-Roi.</t>
+          <t>Dùng Đài Thiên Văn Spacetrek để phát tín hiệu điều khiển, điều chỉnh Mảng Dự Báo Bầu Trời nhằm tạo thời tiết mô phỏng trên toàn Lahai-Roi</t>
         </is>
       </c>
       <c r="N430" s="2" t="inlineStr"/>
@@ -30393,7 +30393,7 @@
       </c>
       <c r="M449" s="2" t="inlineStr">
         <is>
-          <t>2x</t>
+          <t>2 lần</t>
         </is>
       </c>
       <c r="N449" s="2" t="inlineStr"/>
@@ -30657,7 +30657,7 @@
       </c>
       <c r="M453" s="2" t="inlineStr">
         <is>
-          <t>Cải thiện độ rõ Dodget của kết cấu khi nhìn ở góc nghiêng, như trên mặt đất và tường, giúp chi tiết ở xa sắc Dodget hơn.</t>
+          <t>Cải thiện độ rõ nét của kết cấu khi nhìn ở góc nghiêng, như trên mặt đất và tường, giúp chi tiết ở xa sắc nét hơn.</t>
         </is>
       </c>
       <c r="N453" s="2" t="inlineStr"/>
@@ -30723,7 +30723,7 @@
       </c>
       <c r="M454" s="2" t="inlineStr">
         <is>
-          <t>Chức năng Super Resolution giúp tăng tốc độ khung hình mà vẫn duy trì chất lượng hình ảnh</t>
+          <t>Chức năng Siêu Độ Phân Giải giúp tăng tốc khung hình mà vẫn giữ nguyên chất lượng hình ảnh</t>
         </is>
       </c>
       <c r="N454" s="2" t="inlineStr"/>
@@ -30789,7 +30789,7 @@
       </c>
       <c r="M455" s="2" t="inlineStr">
         <is>
-          <t>Chức năng Super Resolution giúp tăng cường chi tiết hình ảnh</t>
+          <t>Chức năng Siêu Độ Phân Giải giúp làm nổi bật chi tiết hình ảnh</t>
         </is>
       </c>
       <c r="N455" s="2" t="inlineStr"/>
@@ -30855,7 +30855,7 @@
       </c>
       <c r="M456" s="2" t="inlineStr">
         <is>
-          <t>Chức năng Super Resolution giúp tăng cường chi tiết hình ảnh</t>
+          <t>Chức năng Siêu Độ Phân Giải giúp làm nổi bật chi tiết hình ảnh</t>
         </is>
       </c>
       <c r="N456" s="2" t="inlineStr"/>
@@ -30987,7 +30987,7 @@
       </c>
       <c r="M458" s="2" t="inlineStr">
         <is>
-          <t>Khi bật, một số cảnh hội thoại cốt truyện sẽ sử dụng kiểu phụ đề mới. Hiện chỉ áp dụng cho nội dung Phiên bản 3.3.</t>
+          <t>Khi bật, một số cảnh đối thoại trong cốt truyện sẽ sử dụng kiểu phụ đề mới. Hiện chỉ áp dụng cho nội dung Phiên bản 3.3.</t>
         </is>
       </c>
       <c r="N458" s="2" t="inlineStr"/>
@@ -31053,7 +31053,7 @@
       </c>
       <c r="M459" s="2" t="inlineStr">
         <is>
-          <t>Phụ kiện</t>
+          <t>Trang sức</t>
         </is>
       </c>
       <c r="N459" s="2" t="inlineStr">
@@ -31123,7 +31123,7 @@
       </c>
       <c r="M460" s="2" t="inlineStr">
         <is>
-          <t>Được trang bị trường treo lơ lửng trên không, cho phép người điều khiển lướt qua địa hình phức tạp hơn.</t>
+          <t>Trang bị trường treo lơ lửng trên không, cho phép người sử dụng lướt qua địa hình phức tạp.</t>
         </is>
       </c>
       <c r="N460" s="2" t="inlineStr"/>
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M461" s="2" t="inlineStr">
         <is>
-          <t>Trao đổi</t>
+          <t>Đổi</t>
         </is>
       </c>
       <c r="N461" s="2" t="inlineStr"/>
@@ -31255,7 +31255,7 @@
       </c>
       <c r="M462" s="2" t="inlineStr">
         <is>
-          <t>Trên Những Vì Sao</t>
+          <t>Vượt Trên Những Vì Sao</t>
         </is>
       </c>
       <c r="N462" s="2" t="inlineStr"/>
@@ -31321,7 +31321,7 @@
       </c>
       <c r="M463" s="2" t="inlineStr">
         <is>
-          <t>Một bức ảnh được Đội Bông bí mật chụp lại. Họ đã chứng kiến khoảnh khắc bạn vươn lên đỉnh cao.</t>
+          <t>Bức ảnh bí mật do Đội Gấu Bông chụp. Họ đã chứng kiến khoảnh khắc cậu vươn tới đỉnh cao.</t>
         </is>
       </c>
       <c r="N463" s="2" t="inlineStr"/>
@@ -31387,7 +31387,7 @@
       </c>
       <c r="M464" s="2" t="inlineStr">
         <is>
-          <t>Thiếu Nữ Phước Lành Trầm Tư</t>
+          <t>Thánh Nữ Thiền Định</t>
         </is>
       </c>
       <c r="N464" s="2" t="inlineStr"/>
@@ -31453,7 +31453,7 @@
       </c>
       <c r="M465" s="2" t="inlineStr">
         <is>
-          <t>Phía trước là cảnh đẹp tuyệt vời!</t>
+          <t>Cảnh đẹp phía trước!</t>
         </is>
       </c>
       <c r="N465" s="2" t="inlineStr"/>
@@ -31521,7 +31521,7 @@
       <c r="M466" s="2" t="inlineStr">
         <is>
           <t>Khi nào... mưa ngừng rơi nhỉ?
-...Dù mưa không rơi, tôi vẫn sẽ ở đây cùng cậu.</t>
+...Dù mưa có tạnh, ta vẫn sẽ ở lại đây cùng cậu.</t>
         </is>
       </c>
       <c r="N466" s="2" t="inlineStr"/>
@@ -31587,7 +31587,7 @@
       </c>
       <c r="M467" s="2" t="inlineStr">
         <is>
-          <t>Hương thơm giờ đây đậm đà hơn bởi vinh quang, bởi chiến thắng, bởi cuộc hội ngộ mong đợi đã lâu, và bởi niềm vui cùng tiếng cười của người bên cạnh bạn.</t>
+          <t>Hương thơm giờ đây đậm đà hơn bởi vinh quang, bởi chiến thắng, bởi cuộc hội ngộ chờ đợi đã lâu, và bởi niềm vui cùng tiếng cười của người bên cạnh.</t>
         </is>
       </c>
       <c r="N467" s="2" t="inlineStr"/>
@@ -31653,7 +31653,7 @@
       </c>
       <c r="M468" s="2" t="inlineStr">
         <is>
-          <t>Hương thơm giờ đây đậm đà hơn bởi vinh quang, bởi chiến thắng, bởi cuộc hội ngộ mong đợi đã lâu, và bởi niềm vui cùng tiếng cười của người bên cạnh bạn.</t>
+          <t>Hương thơm giờ đây đậm đà hơn bởi vinh quang, bởi chiến thắng, bởi cuộc hội ngộ chờ đợi đã lâu, và bởi niềm vui cùng tiếng cười của người bên cạnh.</t>
         </is>
       </c>
       <c r="N468" s="2" t="inlineStr"/>
@@ -32531,7 +32531,7 @@
       </c>
       <c r="M481" s="2" t="inlineStr">
         <is>
-          <t>Tiếp Tục Nhiệm Vụ</t>
+          <t>Tiếp tục nhiệm vụ</t>
         </is>
       </c>
       <c r="N481" s="2" t="inlineStr"/>
@@ -32733,7 +32733,7 @@
       </c>
       <c r="M484" s="2" t="inlineStr">
         <is>
-          <t>Xem Mô-đun Mở Rộng Xe Máy Thám Hiểm Mới</t>
+          <t>Xem Mô-đun Mở Rộng mới cho xe máy thám hiểm.</t>
         </is>
       </c>
       <c r="N484" s="2" t="inlineStr"/>
@@ -32799,7 +32799,7 @@
       </c>
       <c r="M485" s="2" t="inlineStr">
         <is>
-          <t>{0} View Mô-đun Mở Rộng mới của xe máy thám hiểm</t>
+          <t>Xem Mô-đun Mở Rộng mới của xe máy thám hiểm</t>
         </is>
       </c>
       <c r="N485" s="2" t="inlineStr"/>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="M486" s="2" t="inlineStr">
         <is>
-          <t>Xem Mô-đun Mở Rộng Mới Của Xe Máy Thám Hiểm</t>
+          <t>Xem Mô-đun Mở Rộng mới của xe máy thám hiểm.</t>
         </is>
       </c>
       <c r="N486" s="2" t="inlineStr"/>
@@ -32931,7 +32931,7 @@
       </c>
       <c r="M487" s="2" t="inlineStr">
         <is>
-          <t>Đã mở khóa Mô-đun Mở Rộng Aerial Tactics</t>
+          <t>Mô-đun Mở Rộng Chiến Thuật Trên Không đã mở khóa</t>
         </is>
       </c>
       <c r="N487" s="2" t="inlineStr"/>
@@ -32997,7 +32997,7 @@
       </c>
       <c r="M488" s="2" t="inlineStr">
         <is>
-          <t>Mô-đun Mở rộng "Aerial Tactics" đã được mở khóa</t>
+          <t>Mô-đun Mở rộng "Chiến thuật Hàng không" đã được mở khóa</t>
         </is>
       </c>
       <c r="N488" s="2" t="inlineStr"/>
@@ -33063,7 +33063,7 @@
       </c>
       <c r="M489" s="2" t="inlineStr">
         <is>
-          <t>Mô-đun Mở rộng "Aerial Tactics" đã được mở khóa</t>
+          <t>Mô-đun Mở rộng "Chiến thuật Hàng không" đã được mở khóa</t>
         </is>
       </c>
       <c r="N489" s="2" t="inlineStr"/>
